--- a/CONTROLES POR COMISSÃO E GESTORES.xlsx
+++ b/CONTROLES POR COMISSÃO E GESTORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29004E44-23AB-4C5C-B281-F2FD893FD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF4ADD-925C-4E92-B17B-B70203201806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -996,299 +996,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2002,6 +1709,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2036,6 +1773,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2069,12 +1836,17 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2089,9 +1861,63 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2125,6 +1951,35 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2163,40 +2018,42 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2218,12 +2075,17 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2238,9 +2100,119 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2273,6 +2245,34 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3160,16 +3160,16 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B55:K70" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" totalsRowDxfId="47" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="46">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="44" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="43" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="42" totalsRowDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="40" totalsRowDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="39" totalsRowDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="38" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="37" totalsRowDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="36" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="27" totalsRowDxfId="26">
       <calculatedColumnFormula>UPPER("Rejane Vasconcelos Cristino")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3178,21 +3178,21 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K50" totalsRowCount="1" headerRowDxfId="35" dataDxfId="33" totalsRowDxfId="31" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K50" totalsRowCount="1" headerRowDxfId="25" dataDxfId="23" totalsRowDxfId="21" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="20">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B35:F49">
     <sortCondition ref="B34:B49"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>

--- a/CONTROLES POR COMISSÃO E GESTORES.xlsx
+++ b/CONTROLES POR COMISSÃO E GESTORES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACF4ADD-925C-4E92-B17B-B70203201806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969A78EE-C31B-4F3A-829E-7963BBE67C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="177">
   <si>
     <t>GESTOR(A)
 ATUANTE</t>
@@ -576,6 +576,24 @@
   </si>
   <si>
     <t>OSVALDO NETO</t>
+  </si>
+  <si>
+    <t>460001/001617/2023</t>
+  </si>
+  <si>
+    <t>IGOR MARTINS</t>
+  </si>
+  <si>
+    <t>NICHOLAS TAVARES / HIGOR GAMA</t>
+  </si>
+  <si>
+    <t>VASSOURAS</t>
+  </si>
+  <si>
+    <t>LUKE</t>
+  </si>
+  <si>
+    <t>HIGOR GAMA</t>
   </si>
 </sst>
 </file>
@@ -847,7 +865,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -958,6 +976,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -996,6 +1017,275 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1030,22 +1320,17 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1055,7 +1340,15 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1089,100 +1382,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1222,37 +1421,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1297,6 +1465,105 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1312,8 +1579,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1323,31 +1589,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -1357,230 +1598,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3158,7 +3175,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B55:K70" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" totalsRowDxfId="47" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B56:K71" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" totalsRowDxfId="47" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="46">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="44"/>
     <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="43" totalsRowDxfId="42"/>
@@ -3178,21 +3195,21 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K50" totalsRowCount="1" headerRowDxfId="25" dataDxfId="23" totalsRowDxfId="21" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="20">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B35:F49">
-    <sortCondition ref="B34:B49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K51" totalsRowCount="1" headerRowDxfId="25" dataDxfId="23" totalsRowDxfId="21" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B35:F50">
+    <sortCondition ref="B34:B50"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="19" totalsRowDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="18" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="17" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="16" totalsRowDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="14" totalsRowDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="13" totalsRowDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="12" totalsRowDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="11" totalsRowDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="10" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3516,7 +3533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -4865,43 +4882,43 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="39" t="s">
-        <v>115</v>
+      <c r="A42" s="38" t="s">
+        <v>171</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>156</v>
+        <v>172</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>173</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="G42" s="27">
-        <v>1.5408999999999999</v>
+        <v>175</v>
+      </c>
+      <c r="G42" s="50">
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K42" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="K42" s="6" t="s">
-        <v>144</v>
-      </c>
     </row>
     <row r="43" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="38" t="s">
-        <v>80</v>
+      <c r="A43" s="39" t="s">
+        <v>115</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>73</v>
@@ -4913,16 +4930,16 @@
         <v>156</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="G43" s="27">
-        <v>0.78459999999999996</v>
+        <v>1.5408999999999999</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>145</v>
@@ -4935,8 +4952,8 @@
       </c>
     </row>
     <row r="44" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="39" t="s">
-        <v>113</v>
+      <c r="A44" s="38" t="s">
+        <v>80</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>73</v>
@@ -4951,13 +4968,13 @@
         <v>87</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G44" s="27">
-        <v>1</v>
+        <v>0.78459999999999996</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>145</v>
@@ -4970,8 +4987,8 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="38" t="s">
-        <v>81</v>
+      <c r="A45" s="39" t="s">
+        <v>113</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>73</v>
@@ -4983,16 +5000,16 @@
         <v>156</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="G45" s="27">
-        <v>0.89959999999999996</v>
+        <v>1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>145</v>
@@ -5003,14 +5020,10 @@
       <c r="K45" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M45" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="N45" s="46"/>
     </row>
     <row r="46" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="39" t="s">
-        <v>82</v>
+      <c r="A46" s="38" t="s">
+        <v>81</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>73</v>
@@ -5022,13 +5035,13 @@
         <v>156</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="G46" s="27">
-        <v>0.97130000000000005</v>
+        <v>0.89959999999999996</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>162</v>
@@ -5042,20 +5055,14 @@
       <c r="K46" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M46" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N46" s="34">
-        <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],M46)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],M46)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],M46)</f>
-        <v>14</v>
-      </c>
+      <c r="M46" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="N46" s="46"/>
     </row>
     <row r="47" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="38" t="s">
-        <v>130</v>
+      <c r="A47" s="39" t="s">
+        <v>82</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>73</v>
@@ -5067,16 +5074,16 @@
         <v>156</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="G47" s="27">
-        <v>0.80789999999999995</v>
+        <v>0.97130000000000005</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>145</v>
@@ -5088,7 +5095,7 @@
         <v>144</v>
       </c>
       <c r="M47" s="21" t="s">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="N47" s="34">
         <f>COUNTIF(Tabela1[GESTOR(A)
@@ -5099,8 +5106,8 @@
       </c>
     </row>
     <row r="48" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="39" t="s">
-        <v>83</v>
+      <c r="A48" s="38" t="s">
+        <v>130</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>73</v>
@@ -5112,16 +5119,16 @@
         <v>156</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="G48" s="27">
-        <v>0.60799999999999998</v>
+        <v>0.80789999999999995</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>145</v>
@@ -5133,19 +5140,19 @@
         <v>144</v>
       </c>
       <c r="M48" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N48" s="34">
         <f>COUNTIF(Tabela1[GESTOR(A)
 ATUANTE],M48)+COUNTIF(Tabela2[GESTOR(A)
 ATUANTE],M48)+COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],M48)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="38" t="s">
-        <v>84</v>
+      <c r="A49" s="39" t="s">
+        <v>83</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>73</v>
@@ -5157,16 +5164,16 @@
         <v>156</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G49" s="27">
-        <v>0.14130000000000001</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>145</v>
@@ -5178,184 +5185,185 @@
         <v>144</v>
       </c>
       <c r="M49" s="21" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="N49" s="34">
         <f>COUNTIF(Tabela1[GESTOR(A)
 ATUANTE],M49)+COUNTIF(Tabela2[GESTOR(A)
 ATUANTE],M49)+COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],M49)</f>
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B50" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="10">
-        <f>SUBTOTAL(103,Tabela3[EMPRESA])</f>
-        <v>15</v>
-      </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
+      <c r="A50" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="G50" s="27">
+        <v>0.14130000000000001</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="M50" s="21" t="s">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="N50" s="34">
         <f>COUNTIF(Tabela1[GESTOR(A)
 ATUANTE],M50)+COUNTIF(Tabela2[GESTOR(A)
 ATUANTE],M50)+COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],M50)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="B51" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="10">
+        <f>SUBTOTAL(103,Tabela3[EMPRESA])</f>
+        <v>16</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="M51" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="N51" s="34">
+        <f>COUNTIF(Tabela1[GESTOR(A)
+ATUANTE],M51)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],M51)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],M51)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="13">
-        <f>COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],B51)</f>
-        <v>1</v>
-      </c>
-      <c r="G51" s="4"/>
-      <c r="M51" s="30"/>
     </row>
     <row r="52" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C52" s="13">
         <f>COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],B52)</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G52" s="4"/>
       <c r="M52" s="30"/>
     </row>
     <row r="53" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D53" s="19"/>
+      <c r="B53" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="13">
+        <f>COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],B53)</f>
+        <v>15</v>
+      </c>
       <c r="G53" s="4"/>
       <c r="M53" s="30"/>
     </row>
-    <row r="54" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="47" t="s">
+    <row r="54" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="D54" s="19"/>
+      <c r="G54" s="4"/>
+      <c r="M54" s="30"/>
+    </row>
+    <row r="55" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="B54" s="48"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="49"/>
-      <c r="L54" s="32"/>
-      <c r="M54" s="45" t="s">
+      <c r="B55" s="48"/>
+      <c r="C55" s="48"/>
+      <c r="D55" s="48"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="32"/>
+      <c r="M55" s="45" t="s">
         <v>169</v>
       </c>
-      <c r="N54" s="45"/>
-      <c r="O54" s="35"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
+      <c r="N55" s="45"/>
+      <c r="O55" s="35"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F55" s="18" t="s">
+      <c r="F56" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G56" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H56" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I55" s="18" t="s">
+      <c r="I56" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="J55" s="18" t="s">
+      <c r="J56" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="K55" s="18" t="s">
+      <c r="K56" s="18" t="s">
         <v>134</v>
-      </c>
-      <c r="L55"/>
-      <c r="M55" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="N55" s="37" cm="1">
-        <f t="array" ref="N55">SUMPRODUCT(IF(ISERROR(FIND(M55, $D$3:$D$69)), 0, 1))</f>
-        <v>12</v>
-      </c>
-      <c r="O55" s="31"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G56" s="28">
-        <v>0.6603</v>
-      </c>
-      <c r="H56" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="L56"/>
       <c r="M56" s="36" t="s">
-        <v>145</v>
+        <v>168</v>
       </c>
       <c r="N56" s="37" cm="1">
-        <f t="array" ref="N56">SUMPRODUCT(IF(ISERROR(FIND(M56, $D$3:$D$69)), 0, 1))</f>
-        <v>19</v>
+        <f t="array" ref="N56">SUMPRODUCT(IF(ISERROR(FIND(M56, $D$3:$D$70)), 0, 1))</f>
+        <v>12</v>
       </c>
       <c r="O56" s="31"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A57" s="41" t="s">
-        <v>50</v>
+      <c r="A57" s="40" t="s">
+        <v>49</v>
       </c>
       <c r="B57" s="20" t="s">
         <v>142</v>
@@ -5370,12 +5378,12 @@
         <v>57</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G57" s="28">
-        <v>0.51629999999999998</v>
-      </c>
-      <c r="H57" s="21" t="s">
+        <v>0.6603</v>
+      </c>
+      <c r="H57" s="25" t="s">
         <v>162</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -5385,21 +5393,21 @@
         <v>135</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L57"/>
       <c r="M57" s="36" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N57" s="37" cm="1">
-        <f t="array" ref="N57">SUMPRODUCT(IF(ISERROR(FIND(M57, $D$3:$D$69)), 0, 1))</f>
-        <v>6</v>
+        <f t="array" ref="N57">SUMPRODUCT(IF(ISERROR(FIND(M57, $D$3:$D$70)), 0, 1))</f>
+        <v>19</v>
       </c>
       <c r="O57" s="31"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="40" t="s">
-        <v>126</v>
+      <c r="A58" s="41" t="s">
+        <v>50</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>142</v>
@@ -5408,19 +5416,19 @@
         <v>1</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="G58" s="28">
-        <v>0.99219999999999997</v>
+        <v>0.51629999999999998</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>153</v>
@@ -5432,18 +5440,18 @@
         <v>135</v>
       </c>
       <c r="L58"/>
-      <c r="M58" s="36" t="s">
-        <v>141</v>
+      <c r="M58" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="N58" s="37" cm="1">
-        <f t="array" ref="N58">SUMPRODUCT(IF(ISERROR(FIND(M58, $D$3:$D$69)), 0, 1))</f>
-        <v>6</v>
+        <f t="array" ref="N58">SUMPRODUCT(IF(ISERROR(FIND(M58, $D$3:$D$70)), 0, 1))</f>
+        <v>1</v>
       </c>
       <c r="O58" s="31"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="41" t="s">
-        <v>128</v>
+      <c r="A59" s="40" t="s">
+        <v>126</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>142</v>
@@ -5452,16 +5460,16 @@
         <v>1</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="G59" s="28">
-        <v>0.99539999999999995</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="H59" s="21" t="s">
         <v>163</v>
@@ -5477,17 +5485,17 @@
       </c>
       <c r="L59"/>
       <c r="M59" s="36" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="N59" s="37" cm="1">
-        <f t="array" ref="N59">SUMPRODUCT(IF(ISERROR(FIND(M59, $D$3:$D$69)), 0, 1))</f>
-        <v>15</v>
+        <f t="array" ref="N59">SUMPRODUCT(IF(ISERROR(FIND(M59, $D$3:$D$70)), 0, 1))</f>
+        <v>6</v>
       </c>
       <c r="O59" s="31"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="40" t="s">
-        <v>51</v>
+      <c r="A60" s="41" t="s">
+        <v>128</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>142</v>
@@ -5502,13 +5510,13 @@
         <v>57</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="G60" s="28">
-        <v>0.43519999999999998</v>
+        <v>0.99539999999999995</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>153</v>
@@ -5521,19 +5529,19 @@
       </c>
       <c r="L60"/>
       <c r="M60" s="36" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="N60" s="37" cm="1">
-        <f t="array" ref="N60">SUMPRODUCT(IF(ISERROR(FIND(M60, $D$3:$D$69)), 0, 1))</f>
-        <v>17</v>
+        <f t="array" ref="N60">SUMPRODUCT(IF(ISERROR(FIND(M60, $D$3:$D$70)), 0, 1))</f>
+        <v>6</v>
       </c>
       <c r="O60" s="31"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A61" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="B61" s="5" t="s">
+      <c r="A61" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B61" s="20" t="s">
         <v>142</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -5542,14 +5550,14 @@
       <c r="D61" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>61</v>
+      <c r="E61" s="21" t="s">
+        <v>57</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G61" s="28">
-        <v>0.5958</v>
+        <v>0.43519999999999998</v>
       </c>
       <c r="H61" s="21" t="s">
         <v>162</v>
@@ -5564,18 +5572,18 @@
         <v>135</v>
       </c>
       <c r="L61"/>
-      <c r="M61" s="21" t="s">
-        <v>148</v>
+      <c r="M61" s="36" t="s">
+        <v>167</v>
       </c>
       <c r="N61" s="37" cm="1">
-        <f t="array" ref="N61">SUMPRODUCT(IF(ISERROR(FIND(M61, $D$3:$D$69)), 0, 1))</f>
-        <v>21</v>
+        <f t="array" ref="N61">SUMPRODUCT(IF(ISERROR(FIND(M61, $D$3:$D$70)), 0, 1))</f>
+        <v>15</v>
       </c>
       <c r="O61" s="31"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="40" t="s">
-        <v>53</v>
+      <c r="A62" s="41" t="s">
+        <v>52</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>142</v>
@@ -5587,13 +5595,13 @@
         <v>158</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G62" s="28">
-        <v>0.84209999999999996</v>
+        <v>0.5958</v>
       </c>
       <c r="H62" s="21" t="s">
         <v>162</v>
@@ -5608,81 +5616,80 @@
         <v>135</v>
       </c>
       <c r="L62"/>
-      <c r="M62" s="21" t="s">
-        <v>170</v>
+      <c r="M62" s="36" t="s">
+        <v>153</v>
       </c>
       <c r="N62" s="37" cm="1">
-        <f t="array" ref="N62">SUMPRODUCT(IF(ISERROR(FIND(M62, $D$3:$D$69)), 0, 1))</f>
+        <f t="array" ref="N62">SUMPRODUCT(IF(ISERROR(FIND(M62, $D$3:$D$70)), 0, 1))</f>
+        <v>17</v>
+      </c>
+      <c r="O62" s="31"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="O62" s="31"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C63" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E63" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="F63" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="G63" s="29">
-        <v>0</v>
-      </c>
-      <c r="H63" s="22" t="s">
+      <c r="D63" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G63" s="28">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="H63" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="I63" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" ref="J63:J69" si="0">UPPER("REJANE VASCONCELOS")</f>
-        <v>REJANE VASCONCELOS</v>
-      </c>
-      <c r="K63" s="15" t="s">
+      <c r="I63" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K63" s="6" t="s">
         <v>135</v>
       </c>
       <c r="L63"/>
       <c r="M63" s="21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N63" s="37" cm="1">
-        <f t="array" ref="N63">SUMPRODUCT(IF(ISERROR(FIND(M63, $D$3:$D$69)), 0, 1))</f>
-        <v>13</v>
+        <f t="array" ref="N63">SUMPRODUCT(IF(ISERROR(FIND(M63, $D$3:$D$70)), 0, 1))</f>
+        <v>22</v>
       </c>
       <c r="O63" s="31"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B64" s="17" t="s">
+      <c r="A64" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="17" t="s">
         <v>140</v>
-      </c>
-      <c r="C64" s="16" t="s">
-        <v>141</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>159</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>30</v>
+        <v>143</v>
       </c>
       <c r="G64" s="29">
-        <v>0.85919999999999996</v>
+        <v>0</v>
       </c>
       <c r="H64" s="22" t="s">
         <v>162</v>
@@ -5691,39 +5698,43 @@
         <v>157</v>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J64:J70" si="0">UPPER("REJANE VASCONCELOS")</f>
         <v>REJANE VASCONCELOS</v>
       </c>
       <c r="K64" s="15" t="s">
         <v>135</v>
       </c>
       <c r="L64"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
+      <c r="M64" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="N64" s="37" cm="1">
+        <f t="array" ref="N64">SUMPRODUCT(IF(ISERROR(FIND(M64, $D$3:$D$70)), 0, 1))</f>
+        <v>1</v>
+      </c>
       <c r="O64" s="31"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="B65" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C65" s="17" t="s">
-        <v>140</v>
-      </c>
       <c r="D65" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E65" s="15" t="str">
-        <f>UPPER("Miguel Pereira")</f>
-        <v>MIGUEL PEREIRA</v>
+        <v>159</v>
+      </c>
+      <c r="E65" s="15" t="s">
+        <v>38</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>108</v>
+        <v>30</v>
       </c>
       <c r="G65" s="29">
-        <v>7.0000000000000007E-2</v>
+        <v>0.85919999999999996</v>
       </c>
       <c r="H65" s="22" t="s">
         <v>162</v>
@@ -5739,52 +5750,59 @@
         <v>135</v>
       </c>
       <c r="L65"/>
-      <c r="M65" s="30"/>
-      <c r="N65" s="31"/>
+      <c r="M65" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="N65" s="37" cm="1">
+        <f t="array" ref="N65">SUMPRODUCT(IF(ISERROR(FIND(M65, $D$3:$D$70)), 0, 1))</f>
+        <v>13</v>
+      </c>
       <c r="O65" s="31"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="A66" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="B66" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F66" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="G66" s="28">
-        <v>0.87860000000000005</v>
-      </c>
-      <c r="H66" s="21" t="s">
+      <c r="D66" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66" s="15" t="str">
+        <f>UPPER("Miguel Pereira")</f>
+        <v>MIGUEL PEREIRA</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G66" s="29">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H66" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="I66" s="21" t="s">
+      <c r="I66" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="J66" s="6" t="str">
+      <c r="J66" s="15" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K66" s="6" t="s">
+      <c r="K66" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="M66"/>
+      <c r="L66"/>
+      <c r="M66" s="30"/>
       <c r="N66" s="31"/>
       <c r="O66" s="31"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A67" s="41" t="s">
-        <v>123</v>
+      <c r="A67" s="40" t="s">
+        <v>54</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>141</v>
@@ -5796,13 +5814,13 @@
         <v>159</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G67" s="28">
-        <v>0</v>
+        <v>0.87860000000000005</v>
       </c>
       <c r="H67" s="21" t="s">
         <v>162</v>
@@ -5818,10 +5836,12 @@
         <v>135</v>
       </c>
       <c r="M67"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="40" t="s">
-        <v>55</v>
+      <c r="A68" s="41" t="s">
+        <v>123</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>141</v>
@@ -5833,13 +5853,13 @@
         <v>159</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="G68" s="28">
-        <v>0.97019999999999995</v>
+        <v>0</v>
       </c>
       <c r="H68" s="21" t="s">
         <v>162</v>
@@ -5857,26 +5877,26 @@
       <c r="M68"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A69" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B69" s="8" t="s">
+      <c r="A69" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B69" s="5" t="s">
         <v>141</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D69" s="9" t="s">
+      <c r="D69" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E69" s="9" t="s">
-        <v>68</v>
+      <c r="E69" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G69" s="28">
-        <v>0.31530000000000002</v>
+        <v>0.97019999999999995</v>
       </c>
       <c r="H69" s="21" t="s">
         <v>162</v>
@@ -5894,64 +5914,96 @@
       <c r="M69"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
+      <c r="A70" s="41" t="s">
+        <v>56</v>
+      </c>
       <c r="B70" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G70" s="28">
+        <v>0.31530000000000002</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>162</v>
+      </c>
+      <c r="I70" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="J70" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>REJANE VASCONCELOS</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M70"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A71" s="23"/>
+      <c r="B71" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="14">
+      <c r="C71" s="8"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="14">
         <f>SUBTOTAL(103,Tabela2[EMPRESA])</f>
         <v>14</v>
       </c>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
-      <c r="M70"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B71" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C71" s="13">
-        <f>COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],B71)</f>
-        <v>7</v>
-      </c>
-      <c r="N71" s="31"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+      <c r="M71"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B72" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C72" s="13">
         <f>COUNTIF(Tabela2[GESTOR(A)
 ATUANTE],B72)</f>
+        <v>7</v>
+      </c>
+      <c r="N72" s="31"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B73" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="13">
+        <f>COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],B73)</f>
         <v>6</v>
       </c>
-      <c r="N72" s="31"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="N73" s="31"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
       <c r="N74" s="31"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D75" s="23"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
       <c r="E75"/>
       <c r="F75"/>
       <c r="N75" s="31"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D76" s="23"/>
       <c r="E76"/>
       <c r="F76"/>
       <c r="N76" s="31"/>
@@ -5972,13 +6024,11 @@
       <c r="N79" s="31"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G80" s="4"/>
+      <c r="E80"/>
+      <c r="F80"/>
       <c r="N80" s="31"/>
     </row>
     <row r="81" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B81"/>
-      <c r="C81"/>
-      <c r="D81"/>
       <c r="G81" s="4"/>
       <c r="N81" s="31"/>
     </row>
@@ -5990,6 +6040,9 @@
       <c r="N82" s="31"/>
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
       <c r="G83" s="4"/>
       <c r="N83" s="31"/>
     </row>
@@ -6002,13 +6055,13 @@
       <c r="N85" s="31"/>
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E86"/>
-      <c r="F86"/>
+      <c r="G86" s="4"/>
       <c r="N86" s="31"/>
     </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H90"/>
-      <c r="I90"/>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="N87" s="31"/>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.25">
       <c r="H91"/>
@@ -6038,16 +6091,21 @@
       <c r="H97"/>
       <c r="I97"/>
     </row>
+    <row r="98" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H98"/>
+      <c r="I98"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M6:M8">
-    <sortCondition ref="M6:M8"/>
+  <autoFilter ref="A1:A28" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M47:N51">
+    <sortCondition ref="M47:M51"/>
   </sortState>
   <mergeCells count="5">
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="M55:N55"/>
     <mergeCell ref="A33:K33"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="A55:K55"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6057,8 +6115,7 @@
     <oddFooter>Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="K56:K69" calculatedColumn="1"/>
-    <ignoredError sqref="N55:N63" emptyCellReference="1"/>
+    <ignoredError sqref="K57:K70" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="3">
     <tablePart r:id="rId2"/>

--- a/CONTROLES POR COMISSÃO E GESTORES.xlsx
+++ b/CONTROLES POR COMISSÃO E GESTORES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969A78EE-C31B-4F3A-829E-7963BBE67C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0797956-4206-44C4-8FA6-BB0EB6D1B272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
   </bookViews>
@@ -958,6 +958,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -976,9 +979,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1077,7 +1077,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1097,9 +1097,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1108,7 +1106,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1128,9 +1126,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1139,7 +1135,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1159,9 +1155,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1246,41 +1240,71 @@
         <scheme val="minor"/>
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom/>
       </border>
     </dxf>
@@ -1320,6 +1344,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1353,6 +1407,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1382,6 +1466,37 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1421,6 +1536,37 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1465,6 +1611,37 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1498,6 +1675,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1531,6 +1738,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1579,6 +1816,34 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1598,6 +1863,34 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1726,36 +2019,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1790,17 +2053,45 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1815,126 +2106,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1968,35 +2142,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2035,42 +2180,40 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2092,17 +2235,12 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2117,119 +2255,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2262,34 +2290,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3177,16 +3177,16 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B56:K71" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" totalsRowDxfId="47" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="46">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="27" totalsRowDxfId="26">
+    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="44" totalsRowDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="43" totalsRowDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="42" totalsRowDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="40" totalsRowDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="39" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="38" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="37" totalsRowDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="36" totalsRowDxfId="0">
       <calculatedColumnFormula>UPPER("Rejane Vasconcelos Cristino")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3195,21 +3195,21 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K51" totalsRowCount="1" headerRowDxfId="25" dataDxfId="23" totalsRowDxfId="21" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K51" totalsRowCount="1" headerRowDxfId="35" dataDxfId="33" totalsRowDxfId="31" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="30">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B35:F50">
     <sortCondition ref="B34:B50"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="19" totalsRowDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="18" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="17" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="16" totalsRowDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="14" totalsRowDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="13" totalsRowDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="12" totalsRowDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="11" totalsRowDxfId="1"/>
-    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="10" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="11" totalsRowDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3555,19 +3555,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
+      <c r="K1" s="45"/>
       <c r="L1" s="32"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -4584,19 +4584,19 @@
       <c r="M32"/>
     </row>
     <row r="33" spans="1:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="44"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
       <c r="L33" s="33"/>
       <c r="M33"/>
     </row>
@@ -4900,7 +4900,7 @@
       <c r="F42" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G42" s="50">
+      <c r="G42" s="44">
         <v>0</v>
       </c>
       <c r="H42" s="6" t="s">
@@ -5055,10 +5055,10 @@
       <c r="K46" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M46" s="46" t="s">
+      <c r="M46" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="N46" s="46"/>
+      <c r="N46" s="47"/>
     </row>
     <row r="47" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="39" t="s">
@@ -5297,24 +5297,24 @@
       <c r="M54" s="30"/>
     </row>
     <row r="55" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="47" t="s">
+      <c r="A55" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="B55" s="48"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="49"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="50"/>
       <c r="L55" s="32"/>
-      <c r="M55" s="45" t="s">
+      <c r="M55" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="N55" s="45"/>
+      <c r="N55" s="46"/>
       <c r="O55" s="35"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/CONTROLES POR COMISSÃO E GESTORES.xlsx
+++ b/CONTROLES POR COMISSÃO E GESTORES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0797956-4206-44C4-8FA6-BB0EB6D1B272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1974116-9747-4B87-B0A6-231EAD520272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="187">
   <si>
     <t>GESTOR(A)
 ATUANTE</t>
@@ -208,9 +208,6 @@
     <t>SANTA LUZIA</t>
   </si>
   <si>
-    <t>BAIXADA</t>
-  </si>
-  <si>
     <t>330018/000694/2021</t>
   </si>
   <si>
@@ -274,13 +271,7 @@
     <t xml:space="preserve">CONPLAN </t>
   </si>
   <si>
-    <t>NORTE</t>
-  </si>
-  <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>SUL</t>
   </si>
   <si>
     <t>JAQUELINE PASTÓRIO</t>
@@ -594,6 +585,45 @@
   </si>
   <si>
     <t>HIGOR GAMA</t>
+  </si>
+  <si>
+    <t>REGIÃO</t>
+  </si>
+  <si>
+    <t>BX</t>
+  </si>
+  <si>
+    <t>REGIAO</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>LUCIANA POSTIÇO / OSWALDO</t>
+  </si>
+  <si>
+    <t>JULIANA BEZERRA</t>
+  </si>
+  <si>
+    <t>LUCIANA POSTIÇO / OTAVIO FEITOSA</t>
+  </si>
+  <si>
+    <t>HIGOR GAMA / OTAVIO FEITOSA</t>
+  </si>
+  <si>
+    <t>JULIANA FERREIRA</t>
+  </si>
+  <si>
+    <t>170026/002665/2021</t>
+  </si>
+  <si>
+    <t>OSVALDO NETO / OTAVIO FEITOSA</t>
+  </si>
+  <si>
+    <t>ENGEPRAT</t>
   </si>
 </sst>
 </file>
@@ -704,7 +734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -849,23 +879,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -927,9 +946,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -961,30 +977,25 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="84">
     <dxf>
       <font>
         <b val="0"/>
@@ -1036,9 +1047,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1077,6 +1086,368 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b/>
         <i val="0"/>
         <strike val="0"/>
@@ -1280,6 +1651,92 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1310,12 +1767,437 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1340,233 +2222,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1611,6 +2266,105 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1626,32 +2380,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1671,226 +2399,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2410,6 +2918,72 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2425,222 +2999,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -2655,37 +3013,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2724,6 +3051,94 @@
     </dxf>
     <dxf>
       <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2739,7 +3154,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2750,246 +3164,9 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3152,64 +3329,68 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}" name="Tabela1" displayName="Tabela1" ref="B2:K29" totalsRowCount="1" headerRowDxfId="77" dataDxfId="75" totalsRowDxfId="73" headerRowBorderDxfId="76" tableBorderDxfId="74" totalsRowBorderDxfId="72">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:F28">
-    <sortCondition ref="B2:B28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}" name="Tabela1" displayName="Tabela1" ref="B1:L29" totalsRowCount="1" headerRowDxfId="83" dataDxfId="81" totalsRowDxfId="79" headerRowBorderDxfId="82" tableBorderDxfId="80" totalsRowBorderDxfId="78">
+  <autoFilter ref="B1:L28" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F28">
+    <sortCondition ref="B1:B28"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{22E98AA9-BD91-48A6-A436-F9B9B588227B}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="71" totalsRowDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{AFF7C428-2785-471D-B4C4-F32605A0518D}" name="GESTOR SUPLENTE" dataDxfId="69" totalsRowDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{7C1C9573-89CB-4484-84F3-EA8644962A97}" name="FISCAL NOMEADO" dataDxfId="67" totalsRowDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{869013C1-BB93-4AFC-A27C-97C8999DD5A2}" name="MUNICIPIO" dataDxfId="65" totalsRowDxfId="64"/>
-    <tableColumn id="5" xr3:uid="{AABBA10F-A07D-4CCB-8ECC-AF1D1AD18308}" name="EMPRESA" totalsRowFunction="custom" dataDxfId="63" totalsRowDxfId="62">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{22E98AA9-BD91-48A6-A436-F9B9B588227B}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="77" totalsRowDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{AFF7C428-2785-471D-B4C4-F32605A0518D}" name="GESTOR SUPLENTE" dataDxfId="76" totalsRowDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{7C1C9573-89CB-4484-84F3-EA8644962A97}" name="FISCAL NOMEADO" dataDxfId="75" totalsRowDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{869013C1-BB93-4AFC-A27C-97C8999DD5A2}" name="MUNICIPIO" dataDxfId="74" totalsRowDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{AABBA10F-A07D-4CCB-8ECC-AF1D1AD18308}" name="EMPRESA" totalsRowFunction="custom" dataDxfId="73" totalsRowDxfId="6">
       <totalsRowFormula>SUBTOTAL(103,Tabela1[FISCAL NOMEADO])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F54AE55A-3B7D-4BAE-B69D-7A84D6FCB20B}" name="%EXEC" dataDxfId="61" totalsRowDxfId="60"/>
-    <tableColumn id="11" xr3:uid="{8009C64F-7DBB-4571-8622-E16488DD84F8}" name="STATUS" dataDxfId="59" totalsRowDxfId="58"/>
-    <tableColumn id="7" xr3:uid="{3B1DB477-9820-4552-B599-318BD8D1E405}" name="FISCAL SUPLENTE" dataDxfId="57" totalsRowDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{38EEE2AB-235C-4BB6-AFA5-AE2F7AC8F8C5}" name="ADM" dataDxfId="55" totalsRowDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{D0DD72A5-2718-4169-999D-E42F4771245F}" name="ADM SUPLENTE" dataDxfId="53" totalsRowDxfId="52"/>
+    <tableColumn id="10" xr3:uid="{F54AE55A-3B7D-4BAE-B69D-7A84D6FCB20B}" name="%EXEC" dataDxfId="72" totalsRowDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{8009C64F-7DBB-4571-8622-E16488DD84F8}" name="STATUS" dataDxfId="71" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{3B1DB477-9820-4552-B599-318BD8D1E405}" name="FISCAL SUPLENTE" dataDxfId="70" totalsRowDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{38EEE2AB-235C-4BB6-AFA5-AE2F7AC8F8C5}" name="ADM" dataDxfId="69" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{D0DD72A5-2718-4169-999D-E42F4771245F}" name="ADM SUPLENTE" dataDxfId="37" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{90725B59-E0E4-40BB-A22C-E139A882997E}" name="REGIÃO" dataDxfId="36" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B56:K71" totalsRowCount="1" headerRowDxfId="51" dataDxfId="49" totalsRowDxfId="47" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="46">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="45" totalsRowDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="44" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="43" totalsRowDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="42" totalsRowDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="40" totalsRowDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="39" totalsRowDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="38" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="37" totalsRowDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="36" totalsRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B55:L70" totalsRowCount="1" headerRowDxfId="68" dataDxfId="66" totalsRowDxfId="64" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="63">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="62" totalsRowDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="61" totalsRowDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="60" totalsRowDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="59" totalsRowDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="58" totalsRowDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="57" totalsRowDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="56" totalsRowDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="55" totalsRowDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="54" totalsRowDxfId="13"/>
+    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="53" totalsRowDxfId="12">
       <calculatedColumnFormula>UPPER("Rejane Vasconcelos Cristino")</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="3" xr3:uid="{F5130F37-DBCF-45A6-A6F2-A0D5D93F0713}" name="REGIAO" dataDxfId="22" totalsRowDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B34:K51" totalsRowCount="1" headerRowDxfId="35" dataDxfId="33" totalsRowDxfId="31" headerRowBorderDxfId="34" tableBorderDxfId="32" totalsRowBorderDxfId="30">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B35:F50">
-    <sortCondition ref="B34:B50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B33:L50" totalsRowCount="1" headerRowDxfId="52" dataDxfId="50" totalsRowDxfId="48" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:F49">
+    <sortCondition ref="B33:B49"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="11" totalsRowDxfId="10"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="46" totalsRowDxfId="35"/>
+    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="45" totalsRowDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="44" totalsRowDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="43" totalsRowDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="42" totalsRowDxfId="31"/>
+    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="41" totalsRowDxfId="30"/>
+    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="40" totalsRowDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="39" totalsRowDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="38" totalsRowDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="24" totalsRowDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{FC656C22-8A18-474F-B0C5-65DF236ED849}" name="REGIAO" dataDxfId="23" totalsRowDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3533,7 +3714,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:O98"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -3546,257 +3727,299 @@
     <col min="8" max="8" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="19.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5703125" style="4" customWidth="1"/>
-    <col min="13" max="13" width="37.85546875" style="4" customWidth="1"/>
-    <col min="14" max="14" width="3" style="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.140625" style="30" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="4"/>
+    <col min="12" max="12" width="7" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" customWidth="1"/>
+    <col min="14" max="14" width="37.85546875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="3" style="30" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.140625" style="30" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="32"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="L1" s="18" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="27">
+        <v>0.25580000000000003</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L2"/>
-    </row>
-    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="L2" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>146</v>
+        <v>137</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="G3" s="27">
-        <v>0.25580000000000003</v>
+        <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="39" t="s">
-        <v>5</v>
+        <v>180</v>
+      </c>
+      <c r="L3" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>146</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="G4" s="27">
-        <v>0</v>
+        <v>0.99670000000000003</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L4" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="27">
-        <v>0.99670000000000003</v>
+        <v>0.97860000000000003</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="39" t="s">
-        <v>7</v>
+        <v>132</v>
+      </c>
+      <c r="L5" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5" s="31"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>146</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="27">
-        <v>0.97860000000000003</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="M6"/>
-      <c r="N6" s="31"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L6" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="N6"/>
+      <c r="O6" s="31"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" s="27">
-        <v>1.6500000000000001E-2</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="M7"/>
-      <c r="N7" s="31"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="39" t="s">
-        <v>9</v>
+        <v>132</v>
+      </c>
+      <c r="L7" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7" s="31"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
+        <v>10</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>25</v>
@@ -3805,414 +4028,448 @@
         <v>32</v>
       </c>
       <c r="G8" s="27">
-        <v>0.38669999999999999</v>
+        <v>0.9899</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="M8"/>
-      <c r="N8" s="31"/>
-    </row>
-    <row r="9" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L8" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="27">
-        <v>0.9899</v>
+        <v>3.7699999999999997E-2</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="39" t="s">
-        <v>11</v>
+        <v>132</v>
+      </c>
+      <c r="L9" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>12</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>146</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G10" s="27">
-        <v>3.7699999999999997E-2</v>
+        <v>0.88560000000000005</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L10" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="27">
-        <v>0.88560000000000005</v>
+        <v>0.53190000000000004</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>13</v>
+        <v>132</v>
+      </c>
+      <c r="L11" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="G12" s="27">
-        <v>0.53190000000000004</v>
+        <v>0.1074</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L12" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>146</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G13" s="27">
-        <v>0.1074</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
-        <v>110</v>
+        <v>132</v>
+      </c>
+      <c r="L13" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="37" t="s">
+        <v>93</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="G14" s="27">
-        <v>0.54500000000000004</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L14" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>149</v>
-      </c>
       <c r="E15" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15" s="27">
-        <v>0.64100000000000001</v>
+        <v>0.71809999999999996</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
-        <v>97</v>
+        <v>141</v>
+      </c>
+      <c r="L15" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>95</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="27">
-        <v>0.71809999999999996</v>
+        <v>0.62</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L16" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G17" s="27">
-        <v>0.62</v>
+        <v>0.2321</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="39" t="s">
-        <v>99</v>
+        <v>141</v>
+      </c>
+      <c r="L17" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="G18" s="27">
-        <v>0.2321</v>
+        <v>1</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="L18" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G19" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>148</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="39" t="s">
-        <v>17</v>
+        <v>141</v>
+      </c>
+      <c r="L19" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>1</v>
@@ -4221,284 +4478,308 @@
         <v>147</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G20" s="27">
-        <v>0</v>
+        <v>0.78049999999999997</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L20" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G21" s="27">
-        <v>0.78049999999999997</v>
+        <v>119</v>
+      </c>
+      <c r="G21" s="26">
+        <v>0.5</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>148</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="39" t="s">
-        <v>121</v>
+        <v>141</v>
+      </c>
+      <c r="L21" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="37" t="s">
+        <v>115</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="26">
-        <v>0.5</v>
+        <v>114</v>
+      </c>
+      <c r="G22" s="27">
+        <v>1</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>135</v>
+        <v>183</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L22" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>117</v>
+        <v>42</v>
       </c>
       <c r="G23" s="27">
-        <v>1</v>
+        <v>0.7903</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>145</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="39" t="s">
-        <v>19</v>
+        <v>141</v>
+      </c>
+      <c r="L23" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" s="37" t="s">
+        <v>20</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D24" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="27">
+        <v>0.78090000000000004</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="27">
-        <v>0.7903</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>135</v>
+      <c r="J24" s="7" t="s">
+        <v>141</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="L24" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="38" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>43</v>
+        <v>106</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G25" s="27">
-        <v>0.78090000000000004</v>
+        <v>0.66039999999999999</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>145</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="39" t="s">
-        <v>111</v>
+        <v>141</v>
+      </c>
+      <c r="L25" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="37" t="s">
+        <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>45</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="G26" s="27">
-        <v>0.66039999999999999</v>
+        <v>0.86519999999999997</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
-        <v>21</v>
+        <v>141</v>
+      </c>
+      <c r="L26" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="37" t="s">
+        <v>184</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>150</v>
+        <v>185</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="G27" s="27">
-        <v>0.86519999999999997</v>
-      </c>
-      <c r="H27" s="6" t="s">
+        <v>0.97040000000000004</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="39" t="s">
+      <c r="J27" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="L27" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="38" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>28</v>
@@ -4510,39 +4791,43 @@
         <v>0.69730000000000003</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L28" s="47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B29" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="12"/>
       <c r="E29" s="9"/>
       <c r="F29" s="10">
         <f>SUBTOTAL(103,Tabela1[FISCAL NOMEADO])</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="10"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
       <c r="K29" s="11"/>
-      <c r="M29"/>
-      <c r="N29" s="31"/>
+      <c r="L29" s="9"/>
+      <c r="N29"/>
       <c r="O29" s="31"/>
-    </row>
-    <row r="30" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P29" s="31"/>
+    </row>
+    <row r="30" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
         <v>1</v>
       </c>
@@ -4556,1534 +4841,1604 @@
       <c r="J30"/>
       <c r="K30"/>
       <c r="L30"/>
-      <c r="M30"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N30"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C31" s="13">
         <f>COUNTIF(Tabela1[GESTOR(A)
 ATUANTE],B31)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H31"/>
       <c r="I31"/>
       <c r="J31"/>
       <c r="K31"/>
       <c r="L31"/>
-      <c r="M31"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="N31"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C32" s="19"/>
       <c r="H32"/>
       <c r="I32"/>
       <c r="J32"/>
       <c r="K32"/>
       <c r="L32"/>
-      <c r="M32"/>
-    </row>
-    <row r="33" spans="1:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A34" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="27">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L34" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A35" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G35" s="27">
+        <v>0.5746</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L35" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A36" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="45"/>
-      <c r="H33" s="45"/>
-      <c r="I33" s="45"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="33"/>
-      <c r="M33"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C34" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="H34" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="J34" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="K34" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="L34"/>
-    </row>
-    <row r="35" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35" s="27">
-        <v>1</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
-        <v>74</v>
-      </c>
       <c r="B36" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>36</v>
+        <v>134</v>
       </c>
       <c r="G36" s="27">
-        <v>0.5746</v>
+        <v>0.84570000000000001</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L36" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="G37" s="27">
-        <v>0.84570000000000001</v>
+        <v>0.99929999999999997</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="39" t="s">
-        <v>76</v>
+        <v>141</v>
+      </c>
+      <c r="L37" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A38" s="37" t="s">
+        <v>74</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G38" s="27">
-        <v>0.99929999999999997</v>
+        <v>0.79930000000000001</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L38" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="38" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="G39" s="27">
-        <v>0.79930000000000001</v>
+        <v>0.30669999999999997</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="39" t="s">
-        <v>78</v>
+        <v>141</v>
+      </c>
+      <c r="L39" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="37" t="s">
+        <v>76</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G40" s="27">
-        <v>0.30669999999999997</v>
+        <v>0.96009999999999995</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="38" t="s">
-        <v>79</v>
+        <v>141</v>
+      </c>
+      <c r="L40" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" s="37" t="s">
+        <v>168</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G41" s="43">
+        <v>0</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L41" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="G41" s="27">
-        <v>0.96009999999999995</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D42" s="24" t="s">
-        <v>173</v>
+      <c r="D42" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="G42" s="44">
-        <v>0</v>
+        <v>113</v>
+      </c>
+      <c r="G42" s="27">
+        <v>1.5408999999999999</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="39" t="s">
-        <v>115</v>
+        <v>141</v>
+      </c>
+      <c r="L42" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" s="37" t="s">
+        <v>77</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="G43" s="27">
-        <v>1.5408999999999999</v>
+        <v>0.78459999999999996</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="L43" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="38" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G44" s="27">
-        <v>0.78459999999999996</v>
+        <v>1</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="39" t="s">
-        <v>113</v>
+        <v>141</v>
+      </c>
+      <c r="L44" s="46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="37" t="s">
+        <v>78</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="G45" s="27">
-        <v>1</v>
+        <v>0.89959999999999996</v>
       </c>
       <c r="H45" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L45" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="N45" s="45" t="s">
         <v>163</v>
       </c>
-      <c r="I45" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J45" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+      <c r="O45" s="45"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="G46" s="27">
-        <v>0.89959999999999996</v>
+        <v>0.97130000000000005</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M46" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="N46" s="47"/>
-    </row>
-    <row r="47" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A47" s="39" t="s">
-        <v>82</v>
+        <v>141</v>
+      </c>
+      <c r="L46" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="N46" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O46" s="33">
+        <f>COUNTIF(Tabela1[GESTOR(A)
+ATUANTE],N46)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N46)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N46)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="37" t="s">
+        <v>127</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="G47" s="27">
-        <v>0.97130000000000005</v>
+        <v>0.80789999999999995</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M47" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="N47" s="34">
+        <v>141</v>
+      </c>
+      <c r="L47" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="N47" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="O47" s="33">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],M47)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],M47)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],M47)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="13.5" x14ac:dyDescent="0.25">
+ATUANTE],N47)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N47)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N47)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="38" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G48" s="27">
-        <v>0.80789999999999995</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M48" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="N48" s="34">
+        <v>141</v>
+      </c>
+      <c r="L48" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="N48" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="O48" s="33">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],M48)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],M48)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],M48)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="39" t="s">
-        <v>83</v>
+ATUANTE],N48)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N48)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N48)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A49" s="37" t="s">
+        <v>81</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="G49" s="27">
-        <v>0.60799999999999998</v>
+        <v>0.14130000000000001</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M49" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="N49" s="34">
+        <v>141</v>
+      </c>
+      <c r="L49" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="N49" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="O49" s="33">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],M49)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],M49)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],M49)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G50" s="27">
-        <v>0.14130000000000001</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M50" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="N50" s="34">
-        <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],M50)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],M50)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],M50)</f>
+ATUANTE],N49)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N49)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N49)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="25"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="10">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B50" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="10">
         <f>SUBTOTAL(103,Tabela3[EMPRESA])</f>
         <v>16</v>
       </c>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="M51" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="N51" s="34">
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="N50" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="O50" s="33">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],M51)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],M51)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],M51)</f>
+ATUANTE],N50)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N50)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N50)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" s="13">
+        <f>COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],B51)</f>
+        <v>1</v>
+      </c>
+      <c r="G51" s="4"/>
+      <c r="N51" s="30"/>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B52" s="6" t="s">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="C52" s="13">
         <f>COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],B52)</f>
+        <v>15</v>
+      </c>
+      <c r="G52" s="4"/>
+      <c r="N52" s="30"/>
+    </row>
+    <row r="53" spans="1:16" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D53" s="19"/>
+      <c r="G53" s="4"/>
+      <c r="N53" s="30"/>
+    </row>
+    <row r="54" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
+      <c r="L54" s="32"/>
+      <c r="N54" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="O54" s="44"/>
+      <c r="P54" s="34"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A55" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="N55" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="O55" s="36" cm="1">
+        <f t="array" ref="O55">SUMPRODUCT(IF(ISERROR(FIND(N55, $D$2:$D$69)), 0, 1))</f>
+        <v>12</v>
+      </c>
+      <c r="P55" s="31"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A56" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G52" s="4"/>
-      <c r="M52" s="30"/>
-    </row>
-    <row r="53" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="13">
-        <f>COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],B53)</f>
-        <v>15</v>
-      </c>
-      <c r="G53" s="4"/>
-      <c r="M53" s="30"/>
-    </row>
-    <row r="54" spans="1:15" ht="13.5" x14ac:dyDescent="0.25">
-      <c r="D54" s="19"/>
-      <c r="G54" s="4"/>
-      <c r="M54" s="30"/>
-    </row>
-    <row r="55" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
-      <c r="F55" s="49"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="K55" s="50"/>
-      <c r="L55" s="32"/>
-      <c r="M55" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="N55" s="46"/>
-      <c r="O55" s="35"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F56" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I56" s="18" t="s">
+      <c r="D56" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G56" s="28">
+        <v>0.6603</v>
+      </c>
+      <c r="H56" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J56" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="J56" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="K56" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="L56"/>
-      <c r="M56" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="N56" s="37" cm="1">
-        <f t="array" ref="N56">SUMPRODUCT(IF(ISERROR(FIND(M56, $D$3:$D$70)), 0, 1))</f>
-        <v>12</v>
-      </c>
-      <c r="O56" s="31"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K56" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L56" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N56" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="O56" s="36" cm="1">
+        <f t="array" ref="O56">SUMPRODUCT(IF(ISERROR(FIND(N56, $D$2:$D$69)), 0, 1))</f>
+        <v>17</v>
+      </c>
+      <c r="P56" s="31"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="40" t="s">
         <v>49</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E57" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F57" s="21" t="s">
         <v>58</v>
       </c>
       <c r="G57" s="28">
-        <v>0.6603</v>
-      </c>
-      <c r="H57" s="25" t="s">
-        <v>162</v>
+        <v>0.51629999999999998</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>159</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="L57"/>
-      <c r="M57" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="N57" s="37" cm="1">
-        <f t="array" ref="N57">SUMPRODUCT(IF(ISERROR(FIND(M57, $D$3:$D$70)), 0, 1))</f>
-        <v>19</v>
-      </c>
-      <c r="O57" s="31"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A58" s="41" t="s">
-        <v>50</v>
+        <v>132</v>
+      </c>
+      <c r="L57" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="O57" s="36" cm="1">
+        <f t="array" ref="O57">SUMPRODUCT(IF(ISERROR(FIND(N57, $D$2:$D$69)), 0, 1))</f>
+        <v>3</v>
+      </c>
+      <c r="P57" s="31"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A58" s="39" t="s">
+        <v>123</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E58" s="21" t="s">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="G58" s="28">
-        <v>0.51629999999999998</v>
+        <v>0.99219999999999997</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L58"/>
-      <c r="M58" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="N58" s="37" cm="1">
-        <f t="array" ref="N58">SUMPRODUCT(IF(ISERROR(FIND(M58, $D$3:$D$70)), 0, 1))</f>
-        <v>1</v>
-      </c>
-      <c r="O58" s="31"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L58" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N58" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="O58" s="36" cm="1">
+        <f t="array" ref="O58">SUMPRODUCT(IF(ISERROR(FIND(N58, $D$2:$D$69)), 0, 1))</f>
+        <v>6</v>
+      </c>
+      <c r="P58" s="31"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E59" s="21" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="G59" s="28">
-        <v>0.99219999999999997</v>
+        <v>0.99539999999999995</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L59"/>
-      <c r="M59" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="N59" s="37" cm="1">
-        <f t="array" ref="N59">SUMPRODUCT(IF(ISERROR(FIND(M59, $D$3:$D$70)), 0, 1))</f>
+        <v>132</v>
+      </c>
+      <c r="L59" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N59" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="O59" s="36" cm="1">
+        <f t="array" ref="O59">SUMPRODUCT(IF(ISERROR(FIND(N59, $D$2:$D$69)), 0, 1))</f>
         <v>6</v>
       </c>
-      <c r="O59" s="31"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="41" t="s">
-        <v>128</v>
+      <c r="P59" s="31"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="39" t="s">
+        <v>50</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E60" s="21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="G60" s="28">
-        <v>0.99539999999999995</v>
+        <v>0.43519999999999998</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K60" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L60"/>
-      <c r="M60" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="N60" s="37" cm="1">
-        <f t="array" ref="N60">SUMPRODUCT(IF(ISERROR(FIND(M60, $D$3:$D$70)), 0, 1))</f>
-        <v>6</v>
-      </c>
-      <c r="O60" s="31"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L60" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N60" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="O60" s="36" cm="1">
+        <f t="array" ref="O60">SUMPRODUCT(IF(ISERROR(FIND(N60, $D$2:$D$69)), 0, 1))</f>
+        <v>15</v>
+      </c>
+      <c r="P60" s="31"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="B61" s="20" t="s">
-        <v>142</v>
+      <c r="B61" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>57</v>
+        <v>155</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G61" s="28">
-        <v>0.43519999999999998</v>
+        <v>0.5958</v>
       </c>
       <c r="H61" s="21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L61"/>
-      <c r="M61" s="36" t="s">
-        <v>167</v>
-      </c>
-      <c r="N61" s="37" cm="1">
-        <f t="array" ref="N61">SUMPRODUCT(IF(ISERROR(FIND(M61, $D$3:$D$70)), 0, 1))</f>
-        <v>15</v>
-      </c>
-      <c r="O61" s="31"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A62" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="L61" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N61" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="O61" s="36" cm="1">
+        <f t="array" ref="O61">SUMPRODUCT(IF(ISERROR(FIND(N61, $D$2:$D$69)), 0, 1))</f>
+        <v>19</v>
+      </c>
+      <c r="P61" s="31"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A62" s="39" t="s">
         <v>52</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G62" s="28">
-        <v>0.5958</v>
+        <v>0.84209999999999996</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L62"/>
-      <c r="M62" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="N62" s="37" cm="1">
-        <f t="array" ref="N62">SUMPRODUCT(IF(ISERROR(FIND(M62, $D$3:$D$70)), 0, 1))</f>
-        <v>17</v>
-      </c>
-      <c r="O62" s="31"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A63" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D63" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="G63" s="28">
-        <v>0.84209999999999996</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="L63"/>
-      <c r="M63" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="L62" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N62" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="O62" s="36" cm="1">
+        <f t="array" ref="O62">SUMPRODUCT(IF(ISERROR(FIND(N62, $D$2:$D$69)), 0, 1))</f>
+        <v>19</v>
+      </c>
+      <c r="P62" s="31"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E63" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G63" s="29">
+        <v>0</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="I63" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="J63" s="15" t="str">
+        <f t="shared" ref="J63:J69" si="0">UPPER("REJANE VASCONCELOS")</f>
+        <v>REJANE VASCONCELOS</v>
+      </c>
+      <c r="K63" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L63" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N63" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="O63" s="36" cm="1">
+        <f t="array" ref="O63">SUMPRODUCT(IF(ISERROR(FIND(N63, $D$2:$D$69)), 0, 1))</f>
+        <v>2</v>
+      </c>
+      <c r="P63" s="31"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G64" s="29">
+        <v>0.85919999999999996</v>
+      </c>
+      <c r="H64" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="I64" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="J64" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v>REJANE VASCONCELOS</v>
+      </c>
+      <c r="K64" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="L64" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N64" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="N63" s="37" cm="1">
-        <f t="array" ref="N63">SUMPRODUCT(IF(ISERROR(FIND(M63, $D$3:$D$70)), 0, 1))</f>
-        <v>22</v>
-      </c>
-      <c r="O63" s="31"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A64" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D64" s="15" t="s">
+      <c r="O64" s="36" cm="1">
+        <f t="array" ref="O64">SUMPRODUCT(IF(ISERROR(FIND(N64, $D$2:$D$69)), 0, 1))</f>
+        <v>14</v>
+      </c>
+      <c r="P64" s="31"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" s="15" t="str">
+        <f>UPPER("Miguel Pereira")</f>
+        <v>MIGUEL PEREIRA</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="G65" s="29">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H65" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="E64" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="G64" s="29">
-        <v>0</v>
-      </c>
-      <c r="H64" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="J64" s="15" t="str">
-        <f t="shared" ref="J64:J70" si="0">UPPER("REJANE VASCONCELOS")</f>
-        <v>REJANE VASCONCELOS</v>
-      </c>
-      <c r="K64" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L64"/>
-      <c r="M64" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="N64" s="37" cm="1">
-        <f t="array" ref="N64">SUMPRODUCT(IF(ISERROR(FIND(M64, $D$3:$D$70)), 0, 1))</f>
-        <v>1</v>
-      </c>
-      <c r="O64" s="31"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A65" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="E65" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="G65" s="29">
-        <v>0.85919999999999996</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>162</v>
-      </c>
       <c r="I65" s="15" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J65" s="15" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L65"/>
-      <c r="M65" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="N65" s="37" cm="1">
-        <f t="array" ref="N65">SUMPRODUCT(IF(ISERROR(FIND(M65, $D$3:$D$70)), 0, 1))</f>
-        <v>13</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="L65" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N65" s="30"/>
       <c r="O65" s="31"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A66" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C66" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E66" s="15" t="str">
-        <f>UPPER("Miguel Pereira")</f>
-        <v>MIGUEL PEREIRA</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="G66" s="29">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H66" s="22" t="s">
-        <v>162</v>
-      </c>
-      <c r="I66" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="J66" s="15" t="str">
+      <c r="P65" s="31"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G66" s="28">
+        <v>0.87860000000000005</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="I66" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="J66" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K66" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="L66"/>
-      <c r="M66" s="30"/>
-      <c r="N66" s="31"/>
+      <c r="K66" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L66" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N66"/>
       <c r="O66" s="31"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P66" s="31"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="40" t="s">
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D67" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="28">
+        <v>0</v>
+      </c>
+      <c r="H67" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="G67" s="28">
-        <v>0.87860000000000005</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>162</v>
-      </c>
       <c r="I67" s="21" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J67" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M67"/>
-      <c r="N67" s="31"/>
-      <c r="O67" s="31"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="41" t="s">
-        <v>123</v>
+        <v>132</v>
+      </c>
+      <c r="L67" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N67"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="39" t="s">
+        <v>54</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D68" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G68" s="28">
+        <v>0.97019999999999995</v>
+      </c>
+      <c r="H68" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="G68" s="28">
-        <v>0</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>162</v>
-      </c>
       <c r="I68" s="21" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J68" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M68"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="L68" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N68"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>141</v>
+      <c r="B69" s="8" t="s">
+        <v>138</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D69" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="28">
+        <v>0.31530000000000002</v>
+      </c>
+      <c r="H69" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="F69" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="G69" s="28">
-        <v>0.97019999999999995</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>162</v>
-      </c>
       <c r="I69" s="21" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J69" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M69"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A70" s="41" t="s">
-        <v>56</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="L69" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="N69"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="23"/>
       <c r="B70" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D70" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="E70" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F70" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="G70" s="28">
-        <v>0.31530000000000002</v>
-      </c>
-      <c r="H70" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="I70" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="J70" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>REJANE VASCONCELOS</v>
-      </c>
-      <c r="K70" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M70"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-      <c r="B71" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C71" s="8"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="14">
+      <c r="C70" s="8"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="14">
         <f>SUBTOTAL(103,Tabela2[EMPRESA])</f>
         <v>14</v>
       </c>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
-      <c r="M71"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
+      <c r="K70" s="9"/>
+      <c r="L70" s="9"/>
+      <c r="N70"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B71" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="13">
+        <f>COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],B71)</f>
+        <v>7</v>
+      </c>
+      <c r="O71" s="31"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B72" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C72" s="13">
         <f>COUNTIF(Tabela2[GESTOR(A)
 ATUANTE],B72)</f>
-        <v>7</v>
-      </c>
-      <c r="N72" s="31"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B73" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C73" s="13">
-        <f>COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],B73)</f>
         <v>6</v>
       </c>
-      <c r="N73" s="31"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N74" s="31"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B75"/>
-      <c r="C75"/>
-      <c r="D75"/>
+      <c r="O72" s="31"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="O73" s="31"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="O74" s="31"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D75" s="23"/>
       <c r="E75"/>
       <c r="F75"/>
-      <c r="N75" s="31"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D76" s="23"/>
+      <c r="O75" s="31"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E76"/>
       <c r="F76"/>
-      <c r="N76" s="31"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O76" s="31"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E77"/>
       <c r="F77"/>
-      <c r="N77" s="31"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O77" s="31"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E78"/>
       <c r="F78"/>
-      <c r="N78" s="31"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O78" s="31"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E79"/>
       <c r="F79"/>
-      <c r="N79" s="31"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="N80" s="31"/>
-    </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O79" s="31"/>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G80" s="4"/>
+      <c r="O80" s="31"/>
+    </row>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
       <c r="G81" s="4"/>
-      <c r="N81" s="31"/>
-    </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O81" s="31"/>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82"/>
       <c r="C82"/>
       <c r="D82"/>
       <c r="G82" s="4"/>
-      <c r="N82" s="31"/>
-    </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B83"/>
-      <c r="C83"/>
-      <c r="D83"/>
+      <c r="O82" s="31"/>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G83" s="4"/>
-      <c r="N83" s="31"/>
-    </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O83" s="31"/>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G84" s="4"/>
-      <c r="N84" s="31"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O84" s="31"/>
+    </row>
+    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G85" s="4"/>
-      <c r="N85" s="31"/>
-    </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G86" s="4"/>
-      <c r="N86" s="31"/>
-    </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="N87" s="31"/>
-    </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="O85" s="31"/>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="O86" s="31"/>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="H90"/>
+      <c r="I90"/>
+    </row>
+    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H91"/>
       <c r="I91"/>
     </row>
-    <row r="92" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H92"/>
       <c r="I92"/>
     </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H93"/>
       <c r="I93"/>
     </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H94"/>
       <c r="I94"/>
     </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H95"/>
       <c r="I95"/>
     </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
       <c r="H96"/>
       <c r="I96"/>
     </row>
@@ -6091,21 +6446,14 @@
       <c r="H97"/>
       <c r="I97"/>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H98"/>
-      <c r="I98"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:A28" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M47:N51">
-    <sortCondition ref="M47:M51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N46:O50">
+    <sortCondition ref="N46:N50"/>
   </sortState>
-  <mergeCells count="5">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="M55:N55"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="A55:K55"/>
+  <mergeCells count="2">
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="N45:O45"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6115,7 +6463,7 @@
     <oddFooter>Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="K57:K70" calculatedColumn="1"/>
+    <ignoredError sqref="K56:K69" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="3">
     <tablePart r:id="rId2"/>

--- a/CONTROLES POR COMISSÃO E GESTORES.xlsx
+++ b/CONTROLES POR COMISSÃO E GESTORES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1974116-9747-4B87-B0A6-231EAD520272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F1602B-9B86-421F-A345-09C14FBF22AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$A$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$33:$A$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -630,7 +630,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -703,6 +703,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -977,19 +984,19 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1047,7 +1054,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1254,7 +1263,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1292,9 +1300,7 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
+        <top/>
         <bottom/>
       </border>
     </dxf>
@@ -1316,149 +1322,24 @@
         <scheme val="minor"/>
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
         <bottom/>
       </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -1468,204 +1349,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1675,36 +1358,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1720,390 +1373,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2527,6 +1796,96 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2561,6 +1920,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2594,33 +1983,6 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -2631,6 +1993,92 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color auto="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
@@ -2650,6 +2098,35 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2688,6 +2165,35 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2716,12 +2222,17 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2736,6 +2247,31 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -2743,12 +2279,17 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
@@ -2763,9 +2304,62 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2798,6 +2392,34 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2918,6 +2540,149 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2951,6 +2716,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2999,6 +2794,37 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3013,6 +2839,37 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3051,16 +2908,22 @@
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3071,9 +2934,64 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3111,6 +3029,37 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3164,9 +3113,67 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3335,62 +3342,62 @@
     <sortCondition ref="B1:B28"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{22E98AA9-BD91-48A6-A436-F9B9B588227B}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="77" totalsRowDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{AFF7C428-2785-471D-B4C4-F32605A0518D}" name="GESTOR SUPLENTE" dataDxfId="76" totalsRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{7C1C9573-89CB-4484-84F3-EA8644962A97}" name="FISCAL NOMEADO" dataDxfId="75" totalsRowDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{869013C1-BB93-4AFC-A27C-97C8999DD5A2}" name="MUNICIPIO" dataDxfId="74" totalsRowDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{AABBA10F-A07D-4CCB-8ECC-AF1D1AD18308}" name="EMPRESA" totalsRowFunction="custom" dataDxfId="73" totalsRowDxfId="6">
+    <tableColumn id="1" xr3:uid="{22E98AA9-BD91-48A6-A436-F9B9B588227B}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="77" totalsRowDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{AFF7C428-2785-471D-B4C4-F32605A0518D}" name="GESTOR SUPLENTE" dataDxfId="75" totalsRowDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{7C1C9573-89CB-4484-84F3-EA8644962A97}" name="FISCAL NOMEADO" dataDxfId="73" totalsRowDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{869013C1-BB93-4AFC-A27C-97C8999DD5A2}" name="MUNICIPIO" dataDxfId="71" totalsRowDxfId="70"/>
+    <tableColumn id="5" xr3:uid="{AABBA10F-A07D-4CCB-8ECC-AF1D1AD18308}" name="EMPRESA" totalsRowFunction="custom" dataDxfId="69" totalsRowDxfId="68">
       <totalsRowFormula>SUBTOTAL(103,Tabela1[FISCAL NOMEADO])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{F54AE55A-3B7D-4BAE-B69D-7A84D6FCB20B}" name="%EXEC" dataDxfId="72" totalsRowDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{8009C64F-7DBB-4571-8622-E16488DD84F8}" name="STATUS" dataDxfId="71" totalsRowDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{3B1DB477-9820-4552-B599-318BD8D1E405}" name="FISCAL SUPLENTE" dataDxfId="70" totalsRowDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{38EEE2AB-235C-4BB6-AFA5-AE2F7AC8F8C5}" name="ADM" dataDxfId="69" totalsRowDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{D0DD72A5-2718-4169-999D-E42F4771245F}" name="ADM SUPLENTE" dataDxfId="37" totalsRowDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{90725B59-E0E4-40BB-A22C-E139A882997E}" name="REGIÃO" dataDxfId="36" totalsRowDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{F54AE55A-3B7D-4BAE-B69D-7A84D6FCB20B}" name="%EXEC" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="11" xr3:uid="{8009C64F-7DBB-4571-8622-E16488DD84F8}" name="STATUS" dataDxfId="65" totalsRowDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{3B1DB477-9820-4552-B599-318BD8D1E405}" name="FISCAL SUPLENTE" dataDxfId="63" totalsRowDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{38EEE2AB-235C-4BB6-AFA5-AE2F7AC8F8C5}" name="ADM" dataDxfId="61" totalsRowDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{D0DD72A5-2718-4169-999D-E42F4771245F}" name="ADM SUPLENTE" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{90725B59-E0E4-40BB-A22C-E139A882997E}" name="REGIÃO" dataDxfId="57" totalsRowDxfId="56"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B55:L70" totalsRowCount="1" headerRowDxfId="68" dataDxfId="66" totalsRowDxfId="64" headerRowBorderDxfId="67" tableBorderDxfId="65" totalsRowBorderDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B55:L70" totalsRowCount="1" headerRowDxfId="55" dataDxfId="53" totalsRowDxfId="51" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="50">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="62" totalsRowDxfId="21"/>
-    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="61" totalsRowDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="60" totalsRowDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="59" totalsRowDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="58" totalsRowDxfId="17"/>
-    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="57" totalsRowDxfId="16"/>
-    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="56" totalsRowDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="55" totalsRowDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="54" totalsRowDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="53" totalsRowDxfId="12">
+    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="31" totalsRowDxfId="30">
       <calculatedColumnFormula>UPPER("Rejane Vasconcelos Cristino")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F5130F37-DBCF-45A6-A6F2-A0D5D93F0713}" name="REGIAO" dataDxfId="22" totalsRowDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{F5130F37-DBCF-45A6-A6F2-A0D5D93F0713}" name="REGIAO" dataDxfId="29" totalsRowDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B33:L50" totalsRowCount="1" headerRowDxfId="52" dataDxfId="50" totalsRowDxfId="48" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B33:L50" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" totalsRowDxfId="23" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="22">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:F49">
     <sortCondition ref="B33:B49"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="46" totalsRowDxfId="35"/>
-    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="45" totalsRowDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="44" totalsRowDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="43" totalsRowDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="42" totalsRowDxfId="31"/>
-    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="41" totalsRowDxfId="30"/>
-    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="40" totalsRowDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="39" totalsRowDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="38" totalsRowDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="24" totalsRowDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{FC656C22-8A18-474F-B0C5-65DF236ED849}" name="REGIAO" dataDxfId="23" totalsRowDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="20" totalsRowDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="19" totalsRowDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="18" totalsRowDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="16" totalsRowDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="15" totalsRowDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="14" totalsRowDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="13" totalsRowDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="12" totalsRowDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{FC656C22-8A18-474F-B0C5-65DF236ED849}" name="REGIAO" dataDxfId="11" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3808,7 +3815,7 @@
       <c r="K2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3846,7 +3853,7 @@
       <c r="K3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="L3" s="47" t="s">
+      <c r="L3" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3884,7 +3891,7 @@
       <c r="K4" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L4" s="47" t="s">
+      <c r="L4" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -3922,7 +3929,7 @@
       <c r="K5" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L5" s="47" t="s">
+      <c r="L5" s="45" t="s">
         <v>175</v>
       </c>
       <c r="N5"/>
@@ -3962,7 +3969,7 @@
       <c r="K6" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L6" s="47" t="s">
+      <c r="L6" s="45" t="s">
         <v>175</v>
       </c>
       <c r="N6"/>
@@ -4002,7 +4009,7 @@
       <c r="K7" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L7" s="47" t="s">
+      <c r="L7" s="45" t="s">
         <v>175</v>
       </c>
       <c r="N7"/>
@@ -4042,7 +4049,7 @@
       <c r="K8" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L8" s="47" t="s">
+      <c r="L8" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4080,7 +4087,7 @@
       <c r="K9" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L9" s="47" t="s">
+      <c r="L9" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4118,7 +4125,7 @@
       <c r="K10" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L10" s="47" t="s">
+      <c r="L10" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4156,7 +4163,7 @@
       <c r="K11" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4194,7 +4201,7 @@
       <c r="K12" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L12" s="47" t="s">
+      <c r="L12" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4232,7 +4239,7 @@
       <c r="K13" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L13" s="47" t="s">
+      <c r="L13" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4270,7 +4277,7 @@
       <c r="K14" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="L14" s="47" t="s">
+      <c r="L14" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4308,7 +4315,7 @@
       <c r="K15" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="47" t="s">
+      <c r="L15" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4346,7 +4353,7 @@
       <c r="K16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="47" t="s">
+      <c r="L16" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4384,7 +4391,7 @@
       <c r="K17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="47" t="s">
+      <c r="L17" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4422,7 +4429,7 @@
       <c r="K18" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="L18" s="47" t="s">
+      <c r="L18" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4460,7 +4467,7 @@
       <c r="K19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="47" t="s">
+      <c r="L19" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4498,7 +4505,7 @@
       <c r="K20" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L20" s="47" t="s">
+      <c r="L20" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4536,7 +4543,7 @@
       <c r="K21" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L21" s="47" t="s">
+      <c r="L21" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4574,7 +4581,7 @@
       <c r="K22" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L22" s="47" t="s">
+      <c r="L22" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4612,7 +4619,7 @@
       <c r="K23" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="47" t="s">
+      <c r="L23" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4650,7 +4657,7 @@
       <c r="K24" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="L24" s="47" t="s">
+      <c r="L24" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4688,7 +4695,7 @@
       <c r="K25" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L25" s="47" t="s">
+      <c r="L25" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4726,7 +4733,7 @@
       <c r="K26" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L26" s="47" t="s">
+      <c r="L26" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4752,7 +4759,7 @@
       <c r="G27" s="27">
         <v>0.97040000000000004</v>
       </c>
-      <c r="H27" s="48" t="s">
+      <c r="H27" s="6" t="s">
         <v>159</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -4764,7 +4771,7 @@
       <c r="K27" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="L27" s="47" t="s">
+      <c r="L27" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4802,7 +4809,7 @@
       <c r="K28" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L28" s="47" t="s">
+      <c r="L28" s="45" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4940,7 +4947,7 @@
       <c r="K34" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L34" s="46" t="s">
+      <c r="L34" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -4978,7 +4985,7 @@
       <c r="K35" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L35" s="46" t="s">
+      <c r="L35" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5016,7 +5023,7 @@
       <c r="K36" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L36" s="46" t="s">
+      <c r="L36" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5054,7 +5061,7 @@
       <c r="K37" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L37" s="46" t="s">
+      <c r="L37" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5092,7 +5099,7 @@
       <c r="K38" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L38" s="46" t="s">
+      <c r="L38" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5130,7 +5137,7 @@
       <c r="K39" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L39" s="46" t="s">
+      <c r="L39" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5168,7 +5175,7 @@
       <c r="K40" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L40" s="46" t="s">
+      <c r="L40" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5176,11 +5183,11 @@
       <c r="A41" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" s="48" t="s">
         <v>70</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="D41" s="24" t="s">
         <v>170</v>
@@ -5206,7 +5213,7 @@
       <c r="K41" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L41" s="46" t="s">
+      <c r="L41" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5244,7 +5251,7 @@
       <c r="K42" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L42" s="46" t="s">
+      <c r="L42" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5282,7 +5289,7 @@
       <c r="K43" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L43" s="46" t="s">
+      <c r="L43" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5320,7 +5327,7 @@
       <c r="K44" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L44" s="46" t="s">
+      <c r="L44" s="44" t="s">
         <v>177</v>
       </c>
     </row>
@@ -5358,13 +5365,13 @@
       <c r="K45" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L45" s="46" t="s">
+      <c r="L45" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="N45" s="45" t="s">
+      <c r="N45" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="O45" s="45"/>
+      <c r="O45" s="47"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="38" t="s">
@@ -5400,7 +5407,7 @@
       <c r="K46" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L46" s="46" t="s">
+      <c r="L46" s="44" t="s">
         <v>177</v>
       </c>
       <c r="N46" s="21" t="s">
@@ -5448,7 +5455,7 @@
       <c r="K47" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L47" s="46" t="s">
+      <c r="L47" s="44" t="s">
         <v>177</v>
       </c>
       <c r="N47" s="21" t="s">
@@ -5496,7 +5503,7 @@
       <c r="K48" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L48" s="46" t="s">
+      <c r="L48" s="44" t="s">
         <v>177</v>
       </c>
       <c r="N48" s="21" t="s">
@@ -5544,7 +5551,7 @@
       <c r="K49" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L49" s="46" t="s">
+      <c r="L49" s="44" t="s">
         <v>177</v>
       </c>
       <c r="N49" s="21" t="s">
@@ -5555,7 +5562,7 @@
 ATUANTE],N49)+COUNTIF(Tabela2[GESTOR(A)
 ATUANTE],N49)+COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],N49)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
@@ -5605,7 +5612,7 @@
       <c r="C52" s="13">
         <f>COUNTIF(Tabela3[GESTOR(A)
 ATUANTE],B52)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G52" s="4"/>
       <c r="N52" s="30"/>
@@ -5627,10 +5634,10 @@
       <c r="J54"/>
       <c r="K54"/>
       <c r="L54" s="32"/>
-      <c r="N54" s="44" t="s">
+      <c r="N54" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="O54" s="44"/>
+      <c r="O54" s="46"/>
       <c r="P54" s="34"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.25">
@@ -5713,7 +5720,7 @@
       <c r="K56" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L56" s="46" t="s">
+      <c r="L56" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N56" s="35" t="s">
@@ -5759,7 +5766,7 @@
       <c r="K57" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L57" s="46" t="s">
+      <c r="L57" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N57" s="6" t="s">
@@ -5805,7 +5812,7 @@
       <c r="K58" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L58" s="46" t="s">
+      <c r="L58" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N58" s="35" t="s">
@@ -5851,7 +5858,7 @@
       <c r="K59" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L59" s="46" t="s">
+      <c r="L59" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N59" s="35" t="s">
@@ -5897,7 +5904,7 @@
       <c r="K60" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L60" s="46" t="s">
+      <c r="L60" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N60" s="35" t="s">
@@ -5943,7 +5950,7 @@
       <c r="K61" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L61" s="46" t="s">
+      <c r="L61" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N61" s="35" t="s">
@@ -5989,7 +5996,7 @@
       <c r="K62" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L62" s="46" t="s">
+      <c r="L62" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N62" s="21" t="s">
@@ -6036,7 +6043,7 @@
       <c r="K63" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="L63" s="46" t="s">
+      <c r="L63" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N63" s="21" t="s">
@@ -6083,7 +6090,7 @@
       <c r="K64" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="L64" s="46" t="s">
+      <c r="L64" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N64" s="21" t="s">
@@ -6131,7 +6138,7 @@
       <c r="K65" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="L65" s="46" t="s">
+      <c r="L65" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N65" s="30"/>
@@ -6173,7 +6180,7 @@
       <c r="K66" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L66" s="46" t="s">
+      <c r="L66" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N66"/>
@@ -6215,7 +6222,7 @@
       <c r="K67" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L67" s="46" t="s">
+      <c r="L67" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N67"/>
@@ -6255,7 +6262,7 @@
       <c r="K68" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L68" s="46" t="s">
+      <c r="L68" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N68"/>
@@ -6295,7 +6302,7 @@
       <c r="K69" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L69" s="46" t="s">
+      <c r="L69" s="44" t="s">
         <v>178</v>
       </c>
       <c r="N69"/>
@@ -6447,7 +6454,7 @@
       <c r="I97"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A28" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}"/>
+  <autoFilter ref="A33:A49" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N46:O50">
     <sortCondition ref="N46:N50"/>
   </sortState>

--- a/CONTROLES POR COMISSÃO E GESTORES.xlsx
+++ b/CONTROLES POR COMISSÃO E GESTORES.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\APRENDIZADO APP\MEDICOES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F1602B-9B86-421F-A345-09C14FBF22AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1EB0993-77B1-4BD3-AB1C-81F7AC4B6473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="454" xr2:uid="{B96EB9A8-6169-46F2-89FD-740783B0C7B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$33:$A$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$A$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="189">
   <si>
     <t>GESTOR(A)
 ATUANTE</t>
@@ -493,34 +493,16 @@
     <t>ARLINDO BASILIO</t>
   </si>
   <si>
-    <t>NICHOLAS TAVARES / ARLINDO BASILIO</t>
-  </si>
-  <si>
-    <t>ARLINDO BASILIO / NICHOLAS TAVARES</t>
-  </si>
-  <si>
     <t>NICHOLAS TAVARES</t>
   </si>
   <si>
-    <t>NICHOLAS TAVARES / OTAVIO FEITOSA</t>
-  </si>
-  <si>
-    <t>ARLINDO BASILIO / OTAVIO FEITOSA</t>
-  </si>
-  <si>
     <t>OTAVIO FEITOSA</t>
   </si>
   <si>
-    <t>NICHOLAS TAVARES / OSVALDO NETO</t>
-  </si>
-  <si>
     <t>LUCIANA POSTIÇO</t>
   </si>
   <si>
     <t>LUCIANA POSTIÇO / NICHOLAS TAVARES</t>
-  </si>
-  <si>
-    <t>LUCIANA POSTIÇO / ARLINDO BASILIO</t>
   </si>
   <si>
     <t>LUCIANA POSTIÇO / LEANDRO RAMOS</t>
@@ -572,12 +554,6 @@
     <t>460001/001617/2023</t>
   </si>
   <si>
-    <t>IGOR MARTINS</t>
-  </si>
-  <si>
-    <t>NICHOLAS TAVARES / HIGOR GAMA</t>
-  </si>
-  <si>
     <t>VASSOURAS</t>
   </si>
   <si>
@@ -602,35 +578,65 @@
     <t>NT</t>
   </si>
   <si>
-    <t>LUCIANA POSTIÇO / OSWALDO</t>
-  </si>
-  <si>
-    <t>JULIANA BEZERRA</t>
-  </si>
-  <si>
-    <t>LUCIANA POSTIÇO / OTAVIO FEITOSA</t>
-  </si>
-  <si>
-    <t>HIGOR GAMA / OTAVIO FEITOSA</t>
-  </si>
-  <si>
     <t>JULIANA FERREIRA</t>
   </si>
   <si>
     <t>170026/002665/2021</t>
   </si>
   <si>
-    <t>OSVALDO NETO / OTAVIO FEITOSA</t>
-  </si>
-  <si>
     <t>ENGEPRAT</t>
+  </si>
+  <si>
+    <t>HIGOR GAMA / JOAO JOSE</t>
+  </si>
+  <si>
+    <t>HIGOR GAMA  / JOAO JOSE</t>
+  </si>
+  <si>
+    <t>330001/001989/2024</t>
+  </si>
+  <si>
+    <t>ANDERSON / OTAVIO FEITOSA</t>
+  </si>
+  <si>
+    <t>JOAO</t>
+  </si>
+  <si>
+    <t>330018/001076/2021</t>
+  </si>
+  <si>
+    <t>170026/001178/2021</t>
+  </si>
+  <si>
+    <t>330018/000424/2021</t>
+  </si>
+  <si>
+    <t>330018/000423/2021</t>
+  </si>
+  <si>
+    <t>ANDERSON</t>
+  </si>
+  <si>
+    <t>330001/001196/2025</t>
+  </si>
+  <si>
+    <t>330001/001238/2025</t>
+  </si>
+  <si>
+    <t>CORDEIRO</t>
+  </si>
+  <si>
+    <t>NATIVIDADE</t>
+  </si>
+  <si>
+    <t>ENEX </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -710,6 +716,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -891,7 +904,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -978,9 +991,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -990,13 +1000,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1125,7 +1156,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1145,9 +1176,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1156,7 +1185,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1176,9 +1205,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1187,7 +1214,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
+        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1207,9 +1234,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1294,14 +1319,166 @@
         <scheme val="minor"/>
       </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1316,11 +1493,46 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1328,7 +1540,180 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom/>
       </border>
     </dxf>
@@ -1362,6 +1747,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1390,6 +1805,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1423,6 +1868,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1452,6 +1927,37 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1491,6 +1997,37 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1535,6 +2072,37 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1568,6 +2136,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1601,6 +2199,36 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -1649,6 +2277,34 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1668,6 +2324,34 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1792,659 +2476,6 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3336,10 +3367,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}" name="Tabela1" displayName="Tabela1" ref="B1:L29" totalsRowCount="1" headerRowDxfId="83" dataDxfId="81" totalsRowDxfId="79" headerRowBorderDxfId="82" tableBorderDxfId="80" totalsRowBorderDxfId="78">
-  <autoFilter ref="B1:L28" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F28">
-    <sortCondition ref="B1:B28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}" name="Tabela1" displayName="Tabela1" ref="B1:L34" totalsRowCount="1" headerRowDxfId="83" dataDxfId="81" totalsRowDxfId="79" headerRowBorderDxfId="82" tableBorderDxfId="80" totalsRowBorderDxfId="78">
+  <autoFilter ref="B1:L33" xr:uid="{27B24437-A950-46C7-AD6F-8F61E71F6C1E}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F33">
+    <sortCondition ref="B1:B33"/>
   </sortState>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{22E98AA9-BD91-48A6-A436-F9B9B588227B}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="77" totalsRowDxfId="76"/>
@@ -3361,43 +3392,43 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B55:L70" totalsRowCount="1" headerRowDxfId="55" dataDxfId="53" totalsRowDxfId="51" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{77490B51-49AC-48CE-B9D3-F5913D37C0FB}" name="Tabela2" displayName="Tabela2" ref="B60:L77" totalsRowCount="1" headerRowDxfId="55" dataDxfId="53" totalsRowDxfId="51" headerRowBorderDxfId="54" tableBorderDxfId="52" totalsRowBorderDxfId="50">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="47" totalsRowDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="31" totalsRowDxfId="30">
+    <tableColumn id="1" xr3:uid="{C168971F-8A1F-4CE0-AB1A-A91564F865A1}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{28D500DA-BD33-447D-801C-1EDBD59B514A}" name="GESTOR SUPLENTE" dataDxfId="20" totalsRowDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{1BC929D7-C79E-4DD8-8692-AEFFFF4E2201}" name="FISCAL NOMEADO" dataDxfId="19" totalsRowDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{6DB822D5-3B20-4BEB-9FA9-33D9AE724FF4}" name="MUNICIPIO" dataDxfId="18" totalsRowDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1DE280A2-C1B5-497D-B2A7-425CC71F3653}" name="EMPRESA" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{95ED015E-6AEE-4CBF-A570-2665B6975A98}" name="%EXEC" dataDxfId="16" totalsRowDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{1C47120A-915F-4E95-BA45-AF0C41018F09}" name="STATUS" dataDxfId="15" totalsRowDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{0C9C4230-87B4-46C7-8DFF-3C0A2F340B11}" name="FISCAL SUPLENTE" dataDxfId="14" totalsRowDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{4E783EA6-0DCE-4695-BBAF-E24638D55153}" name="ADM" dataDxfId="13" totalsRowDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{CE385090-95B6-4F49-A43B-E7EB63C58B59}" name="ADM SUPLENTE" dataDxfId="12" totalsRowDxfId="1">
       <calculatedColumnFormula>UPPER("Rejane Vasconcelos Cristino")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F5130F37-DBCF-45A6-A6F2-A0D5D93F0713}" name="REGIAO" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{F5130F37-DBCF-45A6-A6F2-A0D5D93F0713}" name="REGIAO" dataDxfId="11" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B33:L50" totalsRowCount="1" headerRowDxfId="27" dataDxfId="25" totalsRowDxfId="23" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="22">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B34:F49">
-    <sortCondition ref="B33:B49"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E49DCA8C-BF3E-4A50-9685-635EA2C8AC88}" name="Tabela3" displayName="Tabela3" ref="B38:L55" totalsRowCount="1" headerRowDxfId="49" dataDxfId="47" totalsRowDxfId="45" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="44">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B39:F54">
+    <sortCondition ref="B38:B54"/>
   </sortState>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="21" totalsRowDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="20" totalsRowDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="19" totalsRowDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="18" totalsRowDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="16" totalsRowDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="15" totalsRowDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="14" totalsRowDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="13" totalsRowDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="12" totalsRowDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{FC656C22-8A18-474F-B0C5-65DF236ED849}" name="REGIAO" dataDxfId="11" totalsRowDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{7C167C76-67AF-4A26-8B9A-BCE2A4995E2A}" name="GESTOR(A)_x000a_ATUANTE" totalsRowLabel="Total" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{884CD221-7FDF-449F-BDDC-36A59A961922}" name="GESTOR SUPLENTE" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{4BAEAB60-D8F3-4A1C-A2A7-1AF80D70ECFB}" name="FISCAL NOMEADO" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{92B91F80-B146-424A-9B8F-B3A204D6D240}" name="MUNICIPIO" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{536E627B-103D-43E3-ADF4-5534C1B8AC84}" name="EMPRESA" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="10" xr3:uid="{6244ECFF-D04A-4C9E-9BB6-3E00642A9BA0}" name="%EXEC" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="11" xr3:uid="{E519A9AE-567A-406C-B69A-B1B53C257A70}" name="STATUS" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{682B89AE-0AB9-4B7F-8C3B-66D341320532}" name="FISCAL SUPLENTE" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{B76C21C5-382B-4784-B00B-25BF832EBF82}" name="ADM" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{E184221B-D39C-481A-9EF0-7BBC0BDCFFB3}" name="ADM SUPLENTE" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{FC656C22-8A18-474F-B0C5-65DF236ED849}" name="REGIAO" dataDxfId="23" totalsRowDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3721,7 +3752,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -3763,10 +3794,10 @@
         <v>24</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>129</v>
@@ -3778,11 +3809,11 @@
         <v>131</v>
       </c>
       <c r="L1" s="18" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="46" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -3792,7 +3823,7 @@
         <v>137</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>25</v>
@@ -3804,23 +3835,23 @@
         <v>0.25580000000000003</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J2" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L2" s="45" t="s">
-        <v>175</v>
+      <c r="L2" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="47" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -3829,36 +3860,36 @@
       <c r="C3" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>179</v>
+      <c r="D3" s="24" t="s">
+        <v>177</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G3" s="27">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K3" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="L3" s="45" t="s">
-        <v>175</v>
+      <c r="L3" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="46" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -3868,7 +3899,7 @@
         <v>137</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>28</v>
@@ -3880,23 +3911,23 @@
         <v>0.99670000000000003</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="J4" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K4" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K4" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L4" s="45" t="s">
-        <v>175</v>
+      <c r="L4" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="47" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
@@ -3906,7 +3937,7 @@
         <v>137</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>25</v>
@@ -3918,25 +3949,25 @@
         <v>0.97860000000000003</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J5" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K5" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L5" s="45" t="s">
-        <v>175</v>
+      <c r="L5" s="44" t="s">
+        <v>167</v>
       </c>
       <c r="N5"/>
       <c r="O5" s="31"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="46" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -3946,7 +3977,7 @@
         <v>137</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>31</v>
@@ -3958,26 +3989,26 @@
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L6" s="45" t="s">
-        <v>175</v>
+      <c r="L6" s="44" t="s">
+        <v>167</v>
       </c>
       <c r="N6"/>
       <c r="O6" s="31"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
-        <v>9</v>
+      <c r="A7" s="46" t="s">
+        <v>180</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>1</v>
@@ -3986,38 +4017,30 @@
         <v>137</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="27">
-        <v>0.38669999999999999</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>159</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L7" s="45" t="s">
-        <v>175</v>
+      <c r="L7" s="44" t="s">
+        <v>167</v>
       </c>
       <c r="N7"/>
       <c r="O7" s="31"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
-        <v>10</v>
+      <c r="A8" s="47" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>1</v>
@@ -4026,7 +4049,7 @@
         <v>137</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>25</v>
@@ -4035,27 +4058,29 @@
         <v>32</v>
       </c>
       <c r="G8" s="27">
-        <v>0.9899</v>
+        <v>0.38669999999999999</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L8" s="45" t="s">
-        <v>175</v>
-      </c>
+      <c r="L8" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8" s="31"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
-        <v>11</v>
+      <c r="A9" s="46" t="s">
+        <v>10</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>1</v>
@@ -4064,36 +4089,36 @@
         <v>137</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G9" s="27">
-        <v>3.7699999999999997E-2</v>
+        <v>0.9899</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J9" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L9" s="45" t="s">
-        <v>175</v>
+      <c r="L9" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="37" t="s">
-        <v>12</v>
+      <c r="A10" s="47" t="s">
+        <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>1</v>
@@ -4102,36 +4127,36 @@
         <v>137</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G10" s="27">
-        <v>0.88560000000000005</v>
+        <v>3.7699999999999997E-2</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L10" s="45" t="s">
-        <v>175</v>
+      <c r="L10" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>13</v>
+      <c r="A11" s="46" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>1</v>
@@ -4140,36 +4165,36 @@
         <v>137</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" s="27">
-        <v>0.53190000000000004</v>
+        <v>0.88560000000000005</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L11" s="45" t="s">
-        <v>175</v>
+      <c r="L11" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
-        <v>14</v>
+      <c r="A12" s="47" t="s">
+        <v>13</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>1</v>
@@ -4178,36 +4203,36 @@
         <v>137</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>122</v>
+        <v>36</v>
       </c>
       <c r="G12" s="27">
-        <v>0.1074</v>
+        <v>0.53190000000000004</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J12" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L12" s="45" t="s">
-        <v>175</v>
+      <c r="L12" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
-        <v>107</v>
+      <c r="A13" s="47" t="s">
+        <v>182</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>1</v>
@@ -4216,36 +4241,28 @@
         <v>137</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G13" s="27">
-        <v>0.54500000000000004</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>159</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="49"/>
+      <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K13" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L13" s="45" t="s">
-        <v>175</v>
+      <c r="L13" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="37" t="s">
-        <v>93</v>
+      <c r="A14" s="46" t="s">
+        <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>1</v>
@@ -4254,188 +4271,172 @@
         <v>137</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>37</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="G14" s="27">
-        <v>0.64100000000000001</v>
+        <v>0.1074</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K14" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L14" s="45" t="s">
-        <v>175</v>
+      <c r="L14" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
-        <v>94</v>
+      <c r="A15" s="46" t="s">
+        <v>181</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="D15" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="G15" s="27">
-        <v>0.71809999999999996</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>159</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L15" s="45" t="s">
-        <v>175</v>
+      <c r="L15" s="44" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>95</v>
+      <c r="A16" s="47" t="s">
+        <v>107</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="D16" s="24" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="G16" s="27">
-        <v>0.62</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
-        <v>96</v>
+      <c r="L16" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>179</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="D17" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="27">
-        <v>0.2321</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>159</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L17" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>15</v>
+      <c r="L17" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="46" t="s">
+        <v>93</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>1</v>
-      </c>
       <c r="D18" s="24" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="G18" s="27">
-        <v>1</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="L18" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L18" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="38" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>137</v>
@@ -4443,37 +4444,37 @@
       <c r="C19" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="s">
-        <v>144</v>
+      <c r="D19" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="G19" s="27">
-        <v>0</v>
+        <v>0.71809999999999996</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L19" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L19" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>137</v>
@@ -4482,36 +4483,36 @@
         <v>1</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="G20" s="27">
-        <v>0.78049999999999997</v>
+        <v>0.62</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L20" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L20" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="38" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>137</v>
@@ -4520,36 +4521,36 @@
         <v>1</v>
       </c>
       <c r="D21" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="27">
+        <v>0.2321</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="G21" s="26">
-        <v>0.5</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>148</v>
-      </c>
       <c r="J21" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L21" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="37" t="s">
-        <v>115</v>
+      <c r="L21" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>15</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>137</v>
@@ -4558,36 +4559,36 @@
         <v>1</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
       <c r="G22" s="27">
         <v>1</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K22" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K22" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L22" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>19</v>
+      <c r="L22" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>17</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>137</v>
@@ -4596,36 +4597,36 @@
         <v>1</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G23" s="27">
-        <v>0.7903</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L23" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" s="37" t="s">
-        <v>20</v>
+      <c r="L23" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>18</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>137</v>
@@ -4634,36 +4635,36 @@
         <v>1</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G24" s="27">
-        <v>0.78090000000000004</v>
+        <v>0.78049999999999997</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J24" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="L24" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
-        <v>108</v>
+      <c r="L24" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="46" t="s">
+        <v>176</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>137</v>
@@ -4672,36 +4673,28 @@
         <v>1</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="27">
-        <v>0.66039999999999999</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>159</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L25" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="37" t="s">
-        <v>21</v>
+      <c r="L25" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="47" t="s">
+        <v>118</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>137</v>
@@ -4710,36 +4703,36 @@
         <v>1</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="27">
-        <v>0.86519999999999997</v>
+        <v>119</v>
+      </c>
+      <c r="G26" s="26">
+        <v>0.5</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L26" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="37" t="s">
-        <v>184</v>
+      <c r="L26" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="46" t="s">
+        <v>115</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>137</v>
@@ -4748,36 +4741,36 @@
         <v>1</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="G27" s="27">
-        <v>0.97040000000000004</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="J27" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K27" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="K27" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="L27" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
-        <v>22</v>
+      <c r="L27" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="47" t="s">
+        <v>19</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>137</v>
@@ -4786,347 +4779,347 @@
         <v>1</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G28" s="27">
-        <v>0.69730000000000003</v>
+        <v>0.7903</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="L28" s="45" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="8" t="s">
+      <c r="L28" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="27">
+        <v>0.78090000000000004</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L29" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="27">
+        <v>0.66039999999999999</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L30" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G31" s="27">
+        <v>0.86519999999999997</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L31" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" s="27">
+        <v>0.97040000000000004</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="L32" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="27">
+        <v>0.69730000000000003</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L33" s="44" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="10">
+      <c r="C34" s="9"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="10">
         <f>SUBTOTAL(103,Tabela1[FISCAL NOMEADO])</f>
-        <v>27</v>
-      </c>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="9"/>
-      <c r="N29"/>
-      <c r="O29" s="31"/>
-      <c r="P29" s="31"/>
-    </row>
-    <row r="30" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="9"/>
+      <c r="N34"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+    </row>
+    <row r="35" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C35" s="13">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],B30)</f>
-        <v>13</v>
-      </c>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
-      <c r="N30"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
+ATUANTE],B35)</f>
+        <v>17</v>
+      </c>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="N35"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C36" s="13">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],B31)</f>
-        <v>14</v>
-      </c>
-      <c r="H31"/>
-      <c r="I31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
-      <c r="N31"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C32" s="19"/>
-      <c r="H32"/>
-      <c r="I32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
-      <c r="N32"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+ATUANTE],B36)</f>
+        <v>15</v>
+      </c>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="N36"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C37" s="19"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="N37"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B38" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C38" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D38" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E38" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F38" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G33" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="H33" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="I33" s="18" t="s">
+      <c r="G38" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="I38" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="J33" s="18" t="s">
+      <c r="J38" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="K33" s="18" t="s">
+      <c r="K38" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A34" s="37" t="s">
+      <c r="L38" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B39" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="D39" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G34" s="27">
+      <c r="G39" s="27">
         <v>1</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L34" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G35" s="27">
-        <v>0.5746</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L35" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A36" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G36" s="27">
-        <v>0.84570000000000001</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L36" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G37" s="27">
-        <v>0.99929999999999997</v>
-      </c>
-      <c r="H37" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L37" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="27">
-        <v>0.79930000000000001</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L38" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G39" s="27">
-        <v>0.30669999999999997</v>
-      </c>
       <c r="H39" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I39" s="6" t="s">
         <v>142</v>
@@ -5137,858 +5130,818 @@
       <c r="K39" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L39" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A40" s="37" t="s">
-        <v>76</v>
+      <c r="L39" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="47" t="s">
+        <v>71</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D40" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G40" s="27">
+        <v>0.5746</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="G40" s="27">
-        <v>0.96009999999999995</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="I40" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L40" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A41" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="L40" s="43" t="s">
         <v>169</v>
       </c>
-      <c r="C41" s="48" t="s">
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A41" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D41" s="24" t="s">
-        <v>170</v>
+      <c r="C41" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="G41" s="43">
-        <v>0</v>
+        <v>134</v>
+      </c>
+      <c r="G41" s="27">
+        <v>0.84570000000000001</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>141</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L41" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A42" s="38" t="s">
-        <v>112</v>
+        <v>171</v>
+      </c>
+      <c r="L41" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A42" s="47" t="s">
+        <v>73</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="G42" s="27">
-        <v>1.5408999999999999</v>
+        <v>0.99929999999999997</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L42" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A43" s="37" t="s">
-        <v>77</v>
+        <v>171</v>
+      </c>
+      <c r="L42" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" s="46" t="s">
+        <v>74</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D43" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G43" s="27">
+        <v>0.79930000000000001</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" s="27">
-        <v>0.78459999999999996</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="I43" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L43" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" s="38" t="s">
-        <v>110</v>
+        <v>171</v>
+      </c>
+      <c r="L43" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" s="47" t="s">
+        <v>75</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>84</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="G44" s="27">
-        <v>1</v>
+        <v>0.30669999999999997</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L44" s="44" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A45" s="37" t="s">
-        <v>78</v>
+        <v>171</v>
+      </c>
+      <c r="L44" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" s="46" t="s">
+        <v>76</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D45" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="G45" s="27">
+        <v>0.96009999999999995</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="G45" s="27">
-        <v>0.89959999999999996</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="I45" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K45" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L45" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G46" s="42">
+        <v>0</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J46" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L45" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="N45" s="47" t="s">
-        <v>163</v>
-      </c>
-      <c r="O45" s="47"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A46" s="38" t="s">
-        <v>79</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" s="27">
-        <v>0.97130000000000005</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>132</v>
-      </c>
       <c r="K46" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L46" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="N46" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="O46" s="33">
-        <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],N46)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],N46)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],N46)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" s="37" t="s">
-        <v>127</v>
+        <v>171</v>
+      </c>
+      <c r="L46" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="47" t="s">
+        <v>112</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G47" s="27">
-        <v>0.80789999999999995</v>
+        <v>1.5408999999999999</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L47" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="N47" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="O47" s="33">
-        <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],N47)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],N47)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],N47)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" s="38" t="s">
-        <v>80</v>
+        <v>171</v>
+      </c>
+      <c r="L47" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" s="46" t="s">
+        <v>77</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>1</v>
+        <v>139</v>
       </c>
       <c r="D48" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G48" s="27">
+        <v>0.78459999999999996</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="G48" s="27">
-        <v>0.60799999999999998</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>161</v>
-      </c>
       <c r="I48" s="6" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L48" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="N48" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="O48" s="33">
-        <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],N48)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],N48)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],N48)</f>
-        <v>7</v>
+        <v>171</v>
+      </c>
+      <c r="L48" s="43" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A49" s="37" t="s">
-        <v>81</v>
+      <c r="A49" s="47" t="s">
+        <v>110</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G49" s="27">
         <v>1</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="H49" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L49" s="43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A50" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G50" s="27">
+        <v>0.89959999999999996</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="I50" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L50" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="N50" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="O50" s="51"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A51" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G51" s="27">
+        <v>0.97130000000000005</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L51" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="N51" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="O51" s="33">
+        <f>COUNTIF(Tabela1[GESTOR(A)
+ATUANTE],N51)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N51)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N51)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A52" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="27">
+        <v>0.80789999999999995</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L52" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="N52" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="O52" s="33">
+        <f>COUNTIF(Tabela1[GESTOR(A)
+ATUANTE],N52)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N52)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N52)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A53" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G53" s="27">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L53" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="N53" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="O53" s="33">
+        <f>COUNTIF(Tabela1[GESTOR(A)
+ATUANTE],N53)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N53)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N53)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A54" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F54" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G49" s="27">
+      <c r="G54" s="27">
         <v>0.14130000000000001</v>
       </c>
-      <c r="H49" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K49" s="6" t="s">
+      <c r="H54" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="J54" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="L49" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="N49" s="21" t="s">
+      <c r="K54" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="L54" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="N54" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="O49" s="33">
+      <c r="O54" s="33">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],N49)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],N49)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],N49)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B50" s="25" t="s">
+ATUANTE],N54)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N54)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N54)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B55" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="25"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="10">
+      <c r="C55" s="25"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="10">
         <f>SUBTOTAL(103,Tabela3[EMPRESA])</f>
         <v>16</v>
       </c>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="N50" s="21" t="s">
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="N55" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O55" s="33">
         <f>COUNTIF(Tabela1[GESTOR(A)
-ATUANTE],N50)+COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],N50)+COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],N50)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B51" s="6" t="s">
+ATUANTE],N55)+COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],N55)+COUNTIF(Tabela3[GESTOR(A)
+ATUANTE],N55)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B56" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C51" s="13">
+      <c r="C56" s="13">
         <f>COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],B51)</f>
+ATUANTE],B56)</f>
         <v>1</v>
       </c>
-      <c r="G51" s="4"/>
-      <c r="N51" s="30"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B52" s="6" t="s">
+      <c r="G56" s="4"/>
+      <c r="N56" s="30"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B57" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="C52" s="13">
+      <c r="C57" s="13">
         <f>COUNTIF(Tabela3[GESTOR(A)
-ATUANTE],B52)</f>
-        <v>14</v>
-      </c>
-      <c r="G52" s="4"/>
-      <c r="N52" s="30"/>
-    </row>
-    <row r="53" spans="1:16" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="19"/>
-      <c r="G53" s="4"/>
-      <c r="N53" s="30"/>
-    </row>
-    <row r="54" spans="1:16" ht="24" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="H54"/>
-      <c r="I54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54" s="32"/>
-      <c r="N54" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="O54" s="46"/>
-      <c r="P54" s="34"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
+ATUANTE],B57)</f>
+        <v>15</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="N57" s="30"/>
+    </row>
+    <row r="58" spans="1:16" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D58" s="19"/>
+      <c r="G58" s="4"/>
+      <c r="N58" s="30"/>
+    </row>
+    <row r="59" spans="1:16" ht="24" x14ac:dyDescent="0.25">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
+      <c r="L59" s="32"/>
+      <c r="N59" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="O59" s="50"/>
+      <c r="P59" s="34"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A60" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B60" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C60" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D60" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E60" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F55" s="18" t="s">
+      <c r="F60" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I55" s="18" t="s">
+      <c r="G60" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I60" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="J55" s="18" t="s">
+      <c r="J60" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="K55" s="18" t="s">
+      <c r="K60" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="L55" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="N55" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="O55" s="36" cm="1">
-        <f t="array" ref="O55">SUMPRODUCT(IF(ISERROR(FIND(N55, $D$2:$D$69)), 0, 1))</f>
-        <v>12</v>
-      </c>
-      <c r="P55" s="31"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A56" s="39" t="s">
+      <c r="L60" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="N60" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="O60" s="36" cm="1">
+        <f t="array" ref="O60">SUMPRODUCT(IF(ISERROR(FIND(N60, $D$2:$D$76)), 0, 1))</f>
+        <v>18</v>
+      </c>
+      <c r="P60" s="31"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A61" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E56" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G56" s="28">
-        <v>0.6603</v>
-      </c>
-      <c r="H56" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="L56" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N56" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="O56" s="36" cm="1">
-        <f t="array" ref="O56">SUMPRODUCT(IF(ISERROR(FIND(N56, $D$2:$D$69)), 0, 1))</f>
-        <v>17</v>
-      </c>
-      <c r="P56" s="31"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A57" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="B57" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E57" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F57" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="G57" s="28">
-        <v>0.51629999999999998</v>
-      </c>
-      <c r="H57" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L57" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N57" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="O57" s="36" cm="1">
-        <f t="array" ref="O57">SUMPRODUCT(IF(ISERROR(FIND(N57, $D$2:$D$69)), 0, 1))</f>
-        <v>3</v>
-      </c>
-      <c r="P57" s="31"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="G58" s="28">
-        <v>0.99219999999999997</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L58" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N58" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="O58" s="36" cm="1">
-        <f t="array" ref="O58">SUMPRODUCT(IF(ISERROR(FIND(N58, $D$2:$D$69)), 0, 1))</f>
-        <v>6</v>
-      </c>
-      <c r="P58" s="31"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A59" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F59" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="G59" s="28">
-        <v>0.99539999999999995</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L59" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N59" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="O59" s="36" cm="1">
-        <f t="array" ref="O59">SUMPRODUCT(IF(ISERROR(FIND(N59, $D$2:$D$69)), 0, 1))</f>
-        <v>6</v>
-      </c>
-      <c r="P59" s="31"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A60" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="F60" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G60" s="28">
-        <v>0.43519999999999998</v>
-      </c>
-      <c r="H60" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L60" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N60" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="O60" s="36" cm="1">
-        <f t="array" ref="O60">SUMPRODUCT(IF(ISERROR(FIND(N60, $D$2:$D$69)), 0, 1))</f>
-        <v>15</v>
-      </c>
-      <c r="P60" s="31"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A61" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="20" t="s">
         <v>139</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>60</v>
+        <v>149</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G61" s="28">
-        <v>0.5958</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>159</v>
+        <v>0.6603</v>
+      </c>
+      <c r="H61" s="25" t="s">
+        <v>153</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J61" s="6" t="s">
         <v>132</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L61" s="44" t="s">
-        <v>178</v>
+        <v>141</v>
+      </c>
+      <c r="L61" s="43" t="s">
+        <v>170</v>
       </c>
       <c r="N61" s="35" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="O61" s="36" cm="1">
-        <f t="array" ref="O61">SUMPRODUCT(IF(ISERROR(FIND(N61, $D$2:$D$69)), 0, 1))</f>
-        <v>19</v>
+        <f t="array" ref="O61">SUMPRODUCT(IF(ISERROR(FIND(N61, $D$2:$D$76)), 0, 1))</f>
+        <v>13</v>
       </c>
       <c r="P61" s="31"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A62" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="A62" s="40" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" s="20" t="s">
         <v>139</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>1</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>62</v>
+        <v>149</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>56</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="G62" s="28">
-        <v>0.84209999999999996</v>
+        <v>0.51629999999999998</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>132</v>
@@ -5996,424 +5949,698 @@
       <c r="K62" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L62" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N62" s="21" t="s">
+      <c r="L62" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N62" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="O62" s="36" cm="1">
+        <f t="array" ref="O62">SUMPRODUCT(IF(ISERROR(FIND(N62, $D$2:$D$76)), 0, 1))</f>
+        <v>0</v>
+      </c>
+      <c r="P62" s="31"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A63" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="G63" s="28">
+        <v>0.99219999999999997</v>
+      </c>
+      <c r="H63" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I63" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="O62" s="36" cm="1">
-        <f t="array" ref="O62">SUMPRODUCT(IF(ISERROR(FIND(N62, $D$2:$D$69)), 0, 1))</f>
-        <v>19</v>
-      </c>
-      <c r="P62" s="31"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A63" s="41" t="s">
+      <c r="J63" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L63" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="O63" s="36" cm="1">
+        <f t="array" ref="O63">SUMPRODUCT(IF(ISERROR(FIND(N63, $D$2:$D$76)), 0, 1))</f>
+        <v>16</v>
+      </c>
+      <c r="P63" s="31"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A64" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" s="28">
+        <v>0.99539999999999995</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L64" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N64" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="O64" s="36" cm="1">
+        <f t="array" ref="O64">SUMPRODUCT(IF(ISERROR(FIND(N64, $D$2:$D$76)), 0, 1))</f>
+        <v>5</v>
+      </c>
+      <c r="P64" s="31"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A65" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G65" s="28">
+        <v>0.43519999999999998</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L65" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N65" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="O65" s="36" cm="1">
+        <f t="array" ref="O65">SUMPRODUCT(IF(ISERROR(FIND(N65, $D$2:$D$76)), 0, 1))</f>
+        <v>8</v>
+      </c>
+      <c r="P65" s="31"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A66" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" s="28">
+        <v>0.5958</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L66" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N66" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="O66" s="36" cm="1">
+        <f t="array" ref="O66">SUMPRODUCT(IF(ISERROR(FIND(N66, $D$2:$D$76)), 0, 1))</f>
+        <v>16</v>
+      </c>
+      <c r="P66" s="31"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A67" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="G67" s="28">
+        <v>0.84209999999999996</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="L67" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N67" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="O67" s="36" cm="1">
+        <f t="array" ref="O67">SUMPRODUCT(IF(ISERROR(FIND(N67, $D$2:$D$76)), 0, 1))</f>
+        <v>17</v>
+      </c>
+      <c r="P67" s="31"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A68" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="B63" s="16" t="s">
+      <c r="B68" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C68" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="D63" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E63" s="15" t="s">
+      <c r="D68" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E68" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F68" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G63" s="29">
+      <c r="G68" s="29">
         <v>0</v>
       </c>
-      <c r="H63" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="I63" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" ref="J63:J69" si="0">UPPER("REJANE VASCONCELOS")</f>
+      <c r="H68" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="I68" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="J68" s="15" t="str">
+        <f t="shared" ref="J68:J76" si="0">UPPER("REJANE VASCONCELOS")</f>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K63" s="15" t="s">
+      <c r="K68" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="L63" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N63" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="O63" s="36" cm="1">
-        <f t="array" ref="O63">SUMPRODUCT(IF(ISERROR(FIND(N63, $D$2:$D$69)), 0, 1))</f>
-        <v>2</v>
-      </c>
-      <c r="P63" s="31"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A64" s="42" t="s">
+      <c r="L68" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N68" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="O68" s="36" cm="1">
+        <f t="array" ref="O68">SUMPRODUCT(IF(ISERROR(FIND(N68, $D$2:$D$76)), 0, 1))</f>
+        <v>1</v>
+      </c>
+      <c r="P68" s="31"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A69" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B69" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C64" s="16" t="s">
+      <c r="C69" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G69" s="28">
+        <v>0.85919999999999996</v>
+      </c>
+      <c r="H69" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L69" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N69" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="O69" s="36" cm="1">
+        <f t="array" ref="O69">SUMPRODUCT(IF(ISERROR(FIND(N69, $D$2:$D$76)), 0, 1))</f>
+        <v>0</v>
+      </c>
+      <c r="P69" s="31"/>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A70" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="E70" s="6" t="str">
+        <f>UPPER("Miguel Pereira")</f>
+        <v>MIGUEL PEREIRA</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G70" s="28">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L70" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N70" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="O70" s="36" cm="1">
+        <f t="array" ref="O70">SUMPRODUCT(IF(ISERROR(FIND(N70, $D$2:$D$76)), 0, 1))</f>
+        <v>18</v>
+      </c>
+      <c r="P70" s="31"/>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A71" s="48" t="s">
+        <v>184</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="G71" s="54"/>
+      <c r="H71" s="55"/>
+      <c r="I71" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K71" s="56" t="str">
+        <f t="shared" ref="K71:K72" si="1">UPPER("Rejane Vasconcelos Cristino")</f>
+        <v>REJANE VASCONCELOS CRISTINO</v>
+      </c>
+      <c r="L71" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N71" s="52"/>
+      <c r="O71" s="53"/>
+      <c r="P71" s="31"/>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A72" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="G72" s="54"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K72" s="56" t="str">
+        <f t="shared" si="1"/>
+        <v>REJANE VASCONCELOS CRISTINO</v>
+      </c>
+      <c r="L72" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N72" s="52"/>
+      <c r="O72" s="53"/>
+      <c r="P72" s="31"/>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A73" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F64" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="G64" s="29">
-        <v>0.85919999999999996</v>
-      </c>
-      <c r="H64" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J64" s="15" t="str">
+      <c r="C73" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="G73" s="28">
+        <v>0.87860000000000005</v>
+      </c>
+      <c r="H73" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I73" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="J73" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K64" s="15" t="s">
+      <c r="K73" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L64" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N64" s="21" t="s">
+      <c r="L73" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N73"/>
+      <c r="O73" s="31"/>
+      <c r="P73" s="31"/>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A74" s="40" t="s">
+        <v>120</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F74" s="21" t="s">
+        <v>122</v>
+      </c>
+      <c r="G74" s="28">
+        <v>0</v>
+      </c>
+      <c r="H74" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I74" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="O64" s="36" cm="1">
-        <f t="array" ref="O64">SUMPRODUCT(IF(ISERROR(FIND(N64, $D$2:$D$69)), 0, 1))</f>
-        <v>14</v>
-      </c>
-      <c r="P64" s="31"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="C65" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" s="15" t="str">
-        <f>UPPER("Miguel Pereira")</f>
-        <v>MIGUEL PEREIRA</v>
-      </c>
-      <c r="F65" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="G65" s="29">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="H65" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="J65" s="15" t="str">
+      <c r="J74" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K65" s="15" t="s">
+      <c r="K74" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L65" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N65" s="30"/>
-      <c r="O65" s="31"/>
-      <c r="P65" s="31"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A66" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="L74" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N74"/>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A75" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C75" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F66" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="G66" s="28">
-        <v>0.87860000000000005</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I66" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="J66" s="6" t="str">
+      <c r="D75" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="G75" s="28">
+        <v>0.97019999999999995</v>
+      </c>
+      <c r="H75" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I75" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="J75" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K66" s="6" t="s">
+      <c r="K75" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L66" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N66"/>
-      <c r="O66" s="31"/>
-      <c r="P66" s="31"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A67" s="40" t="s">
-        <v>120</v>
-      </c>
-      <c r="B67" s="5" t="s">
+      <c r="L75" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N75"/>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A76" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C76" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F67" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G67" s="28">
-        <v>0</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I67" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="J67" s="6" t="str">
+      <c r="D76" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E76" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G76" s="28">
+        <v>0.31530000000000002</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="I76" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="J76" s="6" t="str">
         <f t="shared" si="0"/>
         <v>REJANE VASCONCELOS</v>
       </c>
-      <c r="K67" s="6" t="s">
+      <c r="K76" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="L67" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N67"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A68" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="B68" s="5" t="s">
+      <c r="L76" s="43" t="s">
+        <v>170</v>
+      </c>
+      <c r="N76"/>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A77" s="23"/>
+      <c r="B77" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C77" s="8"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="14">
+        <f>SUBTOTAL(103,Tabela2[EMPRESA])</f>
+        <v>16</v>
+      </c>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="N77"/>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B78" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" s="13">
+        <f>COUNTIF(Tabela2[GESTOR(A)
+ATUANTE],B78)</f>
+        <v>9</v>
+      </c>
+      <c r="O78" s="31"/>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B79" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C68" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G68" s="28">
-        <v>0.97019999999999995</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I68" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="J68" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>REJANE VASCONCELOS</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L68" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N68"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A69" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C69" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F69" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G69" s="28">
-        <v>0.31530000000000002</v>
-      </c>
-      <c r="H69" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="I69" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="J69" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v>REJANE VASCONCELOS</v>
-      </c>
-      <c r="K69" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="L69" s="44" t="s">
-        <v>178</v>
-      </c>
-      <c r="N69"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-      <c r="B70" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="14">
-        <f>SUBTOTAL(103,Tabela2[EMPRESA])</f>
-        <v>14</v>
-      </c>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="9"/>
-      <c r="N70"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B71" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C71" s="13">
+      <c r="C79" s="13">
         <f>COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],B71)</f>
-        <v>7</v>
-      </c>
-      <c r="O71" s="31"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B72" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C72" s="13">
-        <f>COUNTIF(Tabela2[GESTOR(A)
-ATUANTE],B72)</f>
-        <v>6</v>
-      </c>
-      <c r="O72" s="31"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="O73" s="31"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="O74" s="31"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="D75" s="23"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="O75" s="31"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="O76" s="31"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="O77" s="31"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="O78" s="31"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E79"/>
-      <c r="F79"/>
+ATUANTE],B79)</f>
+        <v>5</v>
+      </c>
       <c r="O79" s="31"/>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G80" s="4"/>
       <c r="O80" s="31"/>
     </row>
     <row r="81" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B81"/>
       <c r="C81"/>
       <c r="D81"/>
-      <c r="G81" s="4"/>
+      <c r="E81"/>
+      <c r="F81"/>
       <c r="O81" s="31"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="G82" s="4"/>
+      <c r="D82" s="23"/>
+      <c r="E82"/>
+      <c r="F82"/>
       <c r="O82" s="31"/>
     </row>
     <row r="83" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G83" s="4"/>
+      <c r="E83"/>
+      <c r="F83"/>
       <c r="O83" s="31"/>
     </row>
     <row r="84" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G84" s="4"/>
+      <c r="E84"/>
+      <c r="F84"/>
       <c r="O84" s="31"/>
     </row>
     <row r="85" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G85" s="4"/>
+      <c r="E85"/>
+      <c r="F85"/>
       <c r="O85" s="31"/>
     </row>
     <row r="86" spans="2:15" x14ac:dyDescent="0.25">
@@ -6421,46 +6648,81 @@
       <c r="F86"/>
       <c r="O86" s="31"/>
     </row>
+    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="G87" s="4"/>
+      <c r="O87" s="31"/>
+    </row>
+    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="G88" s="4"/>
+      <c r="O88" s="31"/>
+    </row>
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="G89" s="4"/>
+      <c r="O89" s="31"/>
+    </row>
     <row r="90" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H90"/>
-      <c r="I90"/>
+      <c r="G90" s="4"/>
+      <c r="O90" s="31"/>
     </row>
     <row r="91" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H91"/>
-      <c r="I91"/>
+      <c r="G91" s="4"/>
+      <c r="O91" s="31"/>
     </row>
     <row r="92" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H92"/>
-      <c r="I92"/>
+      <c r="G92" s="4"/>
+      <c r="O92" s="31"/>
     </row>
     <row r="93" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H93"/>
-      <c r="I93"/>
-    </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H94"/>
-      <c r="I94"/>
-    </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H95"/>
-      <c r="I95"/>
-    </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H96"/>
-      <c r="I96"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="O93" s="31"/>
     </row>
     <row r="97" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H97"/>
       <c r="I97"/>
     </row>
+    <row r="98" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H98"/>
+      <c r="I98"/>
+    </row>
+    <row r="99" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H99"/>
+      <c r="I99"/>
+    </row>
+    <row r="100" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H100"/>
+      <c r="I100"/>
+    </row>
+    <row r="101" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H101"/>
+      <c r="I101"/>
+    </row>
+    <row r="102" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H102"/>
+      <c r="I102"/>
+    </row>
+    <row r="103" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H103"/>
+      <c r="I103"/>
+    </row>
+    <row r="104" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H104"/>
+      <c r="I104"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A33:A49" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N46:O50">
-    <sortCondition ref="N46:N50"/>
+  <autoFilter ref="A1:A33" xr:uid="{4F61397C-D407-419C-9BDA-C160B3F745EF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N60:O70">
+    <sortCondition ref="N60:N70"/>
   </sortState>
   <mergeCells count="2">
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="N50:O50"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6470,7 +6732,7 @@
     <oddFooter>Página &amp;P de &amp;N</oddFooter>
   </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="K56:K69" calculatedColumn="1"/>
+    <ignoredError sqref="K61:K70 K73:K76" calculatedColumn="1"/>
   </ignoredErrors>
   <tableParts count="3">
     <tablePart r:id="rId2"/>
